--- a/rtss-pre1917/src/main/resources/emigration-1896-1916.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration-1896-1916.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67068DA3-5FDE-42EA-A7BA-4F560D6EAE16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BBD8FF-01FB-46DE-BB25-1A7F529B5B9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="1980" yWindow="1980" windowWidth="19785" windowHeight="18390" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="note-5" sheetId="7" r:id="rId5"/>
     <sheet name="data" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,12 +28,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="200">
   <si>
     <t>Источник: ЦСК, "Ежегодник России" ("Статистический Ежегодник России")</t>
   </si>
@@ -497,12 +492,6 @@
     <t>Баланс чистой иммиграции (иммиграция минус реэмиграция) для фин. лет будет:</t>
   </si>
   <si>
-    <t>Эмиграция из России в различные страны вне Европы ТОЛЬКО через немецкие порты.</t>
-  </si>
-  <si>
-    <t>Эмиграция из России в различные страны.</t>
-  </si>
-  <si>
     <t>Канада</t>
   </si>
   <si>
@@ -643,6 +632,23 @@
   <si>
     <t>NBER, "International Migrations", Volume I : Statistics, сост. W. Willcox, New York, 1929, стр. 261-273 (table 13)</t>
   </si>
+  <si>
+    <t>Эмиграция из России в различные страны вне Европы ТОЛЬКО через немецкие порты, в календарные годы</t>
+  </si>
+  <si>
+    <t>Эмиграция из России в различные страны (для США - по финансовым годам)</t>
+  </si>
+  <si>
+    <t>Эмиграция из России в различные страны (для США - по финансовым годам) с поправкой на более учёт эмиграции</t>
+  </si>
+  <si>
+    <t>из русской Польши (см. приложение № 2 к pre1917.docx/pdf)</t>
+  </si>
+  <si>
+    <t>уточнение
+рус. Польша
+в США</t>
+  </si>
 </sst>
 </file>
 
@@ -653,7 +659,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -727,7 +733,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -799,9 +805,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -812,6 +815,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -830,9 +842,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -870,7 +882,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -976,7 +988,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1118,7 +1130,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1127,24 +1139,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.578125" customWidth="1"/>
-    <col min="3" max="3" width="20.83984375" customWidth="1"/>
-    <col min="4" max="4" width="24.578125" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8">
+    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1156,7 +1168,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>1904</v>
       </c>
@@ -1167,7 +1179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>1906</v>
       </c>
@@ -1178,7 +1190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>1909</v>
       </c>
@@ -1189,7 +1201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>1910</v>
       </c>
@@ -1200,7 +1212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1911</v>
       </c>
@@ -1211,7 +1223,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>1912</v>
       </c>
@@ -1222,7 +1234,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>1913</v>
       </c>
@@ -1233,162 +1245,162 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
@@ -1396,7 +1408,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B60" s="1">
         <v>1896</v>
       </c>
@@ -1404,7 +1416,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B61" s="1">
         <f>B60+1</f>
         <v>1897</v>
@@ -1413,7 +1425,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B62" s="1">
         <f t="shared" ref="B62:B80" si="0">B61+1</f>
         <v>1898</v>
@@ -1422,7 +1434,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B63" s="1">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1431,7 +1443,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B64" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1440,7 +1452,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="2:3">
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1449,7 +1461,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="2:3">
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1458,7 +1470,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="2:3">
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="1">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1467,7 +1479,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:3">
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="1">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -1476,7 +1488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="2:3">
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="1">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -1485,7 +1497,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:3">
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="1">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -1494,7 +1506,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="2:3">
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B71" s="1">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -1503,7 +1515,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="2:3">
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B72" s="1">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -1512,7 +1524,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="2:3">
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B73" s="1">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -1521,7 +1533,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="2:3">
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B74" s="1">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -1530,7 +1542,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="2:3">
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B75" s="1">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -1539,7 +1551,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:3">
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B76" s="1">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -1548,7 +1560,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="2:3">
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B77" s="1">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -1557,7 +1569,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="2:3">
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B78" s="1">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -1566,7 +1578,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="2:3">
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B79" s="1">
         <f t="shared" si="0"/>
         <v>1915</v>
@@ -1575,7 +1587,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="2:3">
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B80" s="1">
         <f t="shared" si="0"/>
         <v>1916</v>
@@ -1584,7 +1596,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B81" s="1">
         <v>1917</v>
       </c>
@@ -1592,22 +1604,22 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B88" s="1">
         <v>1908</v>
       </c>
@@ -1615,7 +1627,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="89" spans="1:3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B89" s="1">
         <f t="shared" ref="B89:B96" si="1">B88+1</f>
         <v>1909</v>
@@ -1624,7 +1636,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="90" spans="1:3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B90" s="1">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -1633,7 +1645,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="91" spans="1:3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B91" s="1">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -1642,7 +1654,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B92" s="1">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -1651,7 +1663,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B93" s="1">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -1660,7 +1672,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="94" spans="1:3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B94" s="1">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -1669,7 +1681,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B95" s="1">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -1678,7 +1690,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B96" s="1">
         <f t="shared" si="1"/>
         <v>1916</v>
@@ -1687,7 +1699,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="97" spans="2:3">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B97" s="1">
         <v>1917</v>
       </c>
@@ -1703,14 +1715,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.41796875" customWidth="1"/>
-    <col min="5" max="5" width="12.41796875" customWidth="1"/>
-    <col min="6" max="6" width="27.15625" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="27.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="43.2">
+    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -1751,7 +1763,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1896</v>
       </c>
@@ -1794,7 +1806,7 @@
         <v>52136</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>1897</v>
@@ -1836,7 +1848,7 @@
         <v>29981</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A22" si="3">A3+1</f>
         <v>1898</v>
@@ -1878,7 +1890,7 @@
         <v>34554</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -1902,7 +1914,7 @@
         <v>57773.68421052632</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -1926,7 +1938,7 @@
         <v>82289.473684210534</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -1950,7 +1962,7 @@
         <v>79218.947368421053</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -1974,7 +1986,7 @@
         <v>98398.947368421053</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -1998,7 +2010,7 @@
         <v>123398.94736842105</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2022,7 +2034,7 @@
         <v>142088.42105263157</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2046,7 +2058,7 @@
         <v>176721.05263157896</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -2070,7 +2082,7 @@
         <v>212135.78947368421</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -2094,7 +2106,7 @@
         <v>256929.47368421053</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -2118,7 +2130,7 @@
         <v>157857.89473684211</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -2142,7 +2154,7 @@
         <v>114497.89473684211</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -2166,7 +2178,7 @@
         <v>180058.94736842107</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -2190,7 +2202,7 @@
         <v>156781.05263157896</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -2214,7 +2226,7 @@
         <v>163951.57894736843</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -2238,7 +2250,7 @@
         <v>292930.5263157895</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -2262,7 +2274,7 @@
         <v>255636.84210526317</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -2286,7 +2298,7 @@
         <v>23910.526315789473</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -2310,7 +2322,7 @@
         <v>2308.4210526315792</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2335,7 +2347,7 @@
         <v>2687088.4210526319</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
@@ -2347,58 +2359,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.578125" customWidth="1"/>
-    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.15625" customWidth="1"/>
-    <col min="4" max="4" width="7.578125" customWidth="1"/>
-    <col min="5" max="5" width="5.68359375" customWidth="1"/>
-    <col min="6" max="6" width="9.578125" customWidth="1"/>
-    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.68359375" customWidth="1"/>
-    <col min="9" max="9" width="7.578125" customWidth="1"/>
-    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" customWidth="1"/>
+    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="9" max="9" width="7.5703125" customWidth="1"/>
+    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.15625" customWidth="1"/>
-    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.41796875" customWidth="1"/>
-    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.42578125" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:35">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:35">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:35">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:35">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2406,7 +2418,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:35">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
       <c r="P9" s="14" t="s">
         <v>71</v>
       </c>
@@ -2439,7 +2451,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:35">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>84</v>
       </c>
@@ -2522,7 +2534,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:35">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1896</v>
       </c>
@@ -2576,7 +2588,7 @@
       </c>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:35">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>1897</v>
@@ -2631,7 +2643,7 @@
       </c>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:35">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A31" si="2">A12+1</f>
         <v>1898</v>
@@ -2686,7 +2698,7 @@
       </c>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:35">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>1899</v>
@@ -2784,7 +2796,7 @@
         <v>4.3528753924899997</v>
       </c>
     </row>
-    <row r="15" spans="1:35">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -2882,7 +2894,7 @@
         <v>5.6415392085457636</v>
       </c>
     </row>
-    <row r="16" spans="1:35">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -2980,7 +2992,7 @@
         <v>2.5448767286540708</v>
       </c>
     </row>
-    <row r="17" spans="1:35">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -3078,7 +3090,7 @@
         <v>3.0960917891717461</v>
       </c>
     </row>
-    <row r="18" spans="1:35">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -3176,7 +3188,7 @@
         <v>1.9799110237312059</v>
       </c>
     </row>
-    <row r="19" spans="1:35">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -3274,7 +3286,7 @@
         <v>1.427190352127677</v>
       </c>
     </row>
-    <row r="20" spans="1:35">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -3372,7 +3384,7 @@
         <v>1.1078286558345642</v>
       </c>
     </row>
-    <row r="21" spans="1:35">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -3470,7 +3482,7 @@
         <v>1.61159938769543</v>
       </c>
     </row>
-    <row r="22" spans="1:35">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -3568,7 +3580,7 @@
         <v>2.650444548432382</v>
       </c>
     </row>
-    <row r="23" spans="1:35">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -3666,7 +3678,7 @@
         <v>1.6072463326115465</v>
       </c>
     </row>
-    <row r="24" spans="1:35">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -3764,7 +3776,7 @@
         <v>1.6887644302205966</v>
       </c>
     </row>
-    <row r="25" spans="1:35">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -3862,7 +3874,7 @@
         <v>2.6865499548398257</v>
       </c>
     </row>
-    <row r="26" spans="1:35">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -3960,7 +3972,7 @@
         <v>1.5918358446542664</v>
       </c>
     </row>
-    <row r="27" spans="1:35">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -4058,7 +4070,7 @@
         <v>1.3100851238884845</v>
       </c>
     </row>
-    <row r="28" spans="1:35">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -4156,7 +4168,7 @@
         <v>2.3027080052662829</v>
       </c>
     </row>
-    <row r="29" spans="1:35">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -4254,7 +4266,7 @@
         <v>2.0608548525781489</v>
       </c>
     </row>
-    <row r="30" spans="1:35">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -4352,7 +4364,7 @@
         <v>0.49870172690928577</v>
       </c>
     </row>
-    <row r="31" spans="1:35">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -4450,7 +4462,7 @@
         <v>1.3926559566033798</v>
       </c>
     </row>
-    <row r="32" spans="1:35">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>1917</v>
       </c>
@@ -4547,7 +4559,7 @@
         <v>5.8184812868690303E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="P33" s="17">
         <f>SUM(P14:P31)-P32</f>
         <v>0</v>
@@ -4590,7 +4602,7 @@
       </c>
       <c r="AI33" s="4"/>
     </row>
-    <row r="34" spans="1:35">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4643,7 +4655,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:35">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4696,12 +4708,12 @@
         <v>0.1375376540970189</v>
       </c>
     </row>
-    <row r="38" spans="1:35">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:35">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>87</v>
       </c>
@@ -4742,10 +4754,10 @@
         <v>81</v>
       </c>
       <c r="O40" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="41" spans="1:35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>1896</v>
       </c>
@@ -4802,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:35">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <f>A41+1</f>
         <v>1897</v>
@@ -4860,7 +4872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <f t="shared" ref="A43:A60" si="17">A42+1</f>
         <v>1898</v>
@@ -4918,7 +4930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <f t="shared" si="17"/>
         <v>1899</v>
@@ -4976,7 +4988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <f t="shared" si="17"/>
         <v>1900</v>
@@ -5034,7 +5046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <f t="shared" si="17"/>
         <v>1901</v>
@@ -5092,7 +5104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <f t="shared" si="17"/>
         <v>1902</v>
@@ -5150,7 +5162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <f t="shared" si="17"/>
         <v>1903</v>
@@ -5208,7 +5220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <f t="shared" si="17"/>
         <v>1904</v>
@@ -5266,7 +5278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <f t="shared" si="17"/>
         <v>1905</v>
@@ -5324,7 +5336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <f t="shared" si="17"/>
         <v>1906</v>
@@ -5382,7 +5394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <f t="shared" si="17"/>
         <v>1907</v>
@@ -5440,7 +5452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <f t="shared" si="17"/>
         <v>1908</v>
@@ -5498,7 +5510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <f t="shared" si="17"/>
         <v>1909</v>
@@ -5556,7 +5568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <f t="shared" si="17"/>
         <v>1910</v>
@@ -5614,7 +5626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <f t="shared" si="17"/>
         <v>1911</v>
@@ -5672,7 +5684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <f t="shared" si="17"/>
         <v>1912</v>
@@ -5730,7 +5742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <f t="shared" si="17"/>
         <v>1913</v>
@@ -5788,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <f t="shared" si="17"/>
         <v>1914</v>
@@ -5846,7 +5858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <f t="shared" si="17"/>
         <v>1915</v>
@@ -5904,7 +5916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>1916</v>
       </c>
@@ -5961,7 +5973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
         <v>49</v>
       </c>
@@ -6018,7 +6030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="11" t="s">
         <v>88</v>
       </c>
@@ -6071,12 +6083,12 @@
         <v>0.12899442300236147</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
         <v>84</v>
       </c>
@@ -6117,7 +6129,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>1908</v>
       </c>
@@ -6159,7 +6171,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <f t="shared" ref="A70:A76" si="39">A69+1</f>
         <v>1909</v>
@@ -6202,7 +6214,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <f t="shared" si="39"/>
         <v>1910</v>
@@ -6245,7 +6257,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <f t="shared" si="39"/>
         <v>1911</v>
@@ -6271,7 +6283,7 @@
       </c>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <f t="shared" si="39"/>
         <v>1912</v>
@@ -6314,7 +6326,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <f t="shared" si="39"/>
         <v>1913</v>
@@ -6340,7 +6352,7 @@
       </c>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <f t="shared" si="39"/>
         <v>1914</v>
@@ -6383,7 +6395,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <f t="shared" si="39"/>
         <v>1915</v>
@@ -6426,16 +6438,16 @@
         <v>78</v>
       </c>
       <c r="P76" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>176</v>
+      </c>
+      <c r="R76" t="s">
         <v>177</v>
       </c>
-      <c r="Q76" t="s">
-        <v>178</v>
-      </c>
-      <c r="R76" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19">
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>1916</v>
       </c>
@@ -6485,7 +6497,7 @@
         <v>1.1658168920416758</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>1917</v>
       </c>
@@ -6512,15 +6524,15 @@
         <v>8961.6344491243617</v>
       </c>
       <c r="S78" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>84</v>
       </c>
@@ -6561,7 +6573,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>1908</v>
       </c>
@@ -6603,7 +6615,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <f t="shared" ref="A84:A90" si="41">A83+1</f>
         <v>1909</v>
@@ -6646,7 +6658,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <f t="shared" si="41"/>
         <v>1910</v>
@@ -6689,7 +6701,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <f t="shared" si="41"/>
         <v>1911</v>
@@ -6715,7 +6727,7 @@
       </c>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <f t="shared" si="41"/>
         <v>1912</v>
@@ -6758,7 +6770,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <f t="shared" si="41"/>
         <v>1913</v>
@@ -6784,7 +6796,7 @@
       </c>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <f t="shared" si="41"/>
         <v>1914</v>
@@ -6827,7 +6839,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <f t="shared" si="41"/>
         <v>1915</v>
@@ -6870,7 +6882,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>1916</v>
       </c>
@@ -6912,7 +6924,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>1917</v>
       </c>
@@ -6937,12 +6949,12 @@
       </c>
       <c r="M92" s="4"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
@@ -6980,7 +6992,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>143</v>
       </c>
@@ -7033,7 +7045,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>144</v>
       </c>
@@ -7086,7 +7098,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>145</v>
       </c>
@@ -7139,7 +7151,7 @@
         <v>54.280155642023345</v>
       </c>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B100" s="26"/>
       <c r="C100" s="26"/>
       <c r="D100" s="26"/>
@@ -7153,9 +7165,9 @@
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B101" s="26"/>
       <c r="C101" s="26"/>
@@ -7170,7 +7182,7 @@
       <c r="L101" s="26"/>
       <c r="M101" s="26"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
       <c r="D102" s="26"/>
@@ -7184,7 +7196,7 @@
       <c r="L102" s="26"/>
       <c r="M102" s="26"/>
     </row>
-    <row r="103" spans="1:13">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B103" s="10" t="s">
         <v>70</v>
       </c>
@@ -7222,7 +7234,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>143</v>
       </c>
@@ -7275,7 +7287,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>144</v>
       </c>
@@ -7328,7 +7340,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>145</v>
       </c>
@@ -7381,7 +7393,7 @@
         <v>47.149894440534837</v>
       </c>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B107" s="26"/>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
@@ -7395,9 +7407,9 @@
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B108" s="26"/>
       <c r="C108" s="26"/>
@@ -7412,9 +7424,9 @@
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B109" s="26"/>
       <c r="C109" s="26"/>
@@ -7429,7 +7441,7 @@
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B110" s="26"/>
       <c r="C110" s="26"/>
       <c r="D110" s="26"/>
@@ -7443,7 +7455,7 @@
       <c r="L110" s="26"/>
       <c r="M110" s="26"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
@@ -7481,7 +7493,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:13">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B112" s="26">
         <f>B106</f>
         <v>6.9984447900466566</v>
@@ -7531,12 +7543,12 @@
         <v>50.715025041279091</v>
       </c>
     </row>
-    <row r="114" spans="1:16">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="116" spans="1:16">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>84</v>
       </c>
@@ -7577,13 +7589,13 @@
         <v>81</v>
       </c>
       <c r="O116" s="10" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="P116" s="10" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="117" spans="1:16">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>1896</v>
       </c>
@@ -7640,7 +7652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <f>A117+1</f>
         <v>1897</v>
@@ -7698,7 +7710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <f t="shared" ref="A119:A137" si="54">A118+1</f>
         <v>1898</v>
@@ -7756,7 +7768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <f t="shared" si="54"/>
         <v>1899</v>
@@ -7814,7 +7826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <f t="shared" si="54"/>
         <v>1900</v>
@@ -7872,7 +7884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <f t="shared" si="54"/>
         <v>1901</v>
@@ -7930,7 +7942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <f t="shared" si="54"/>
         <v>1902</v>
@@ -7988,7 +8000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <f t="shared" si="54"/>
         <v>1903</v>
@@ -8046,7 +8058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <f t="shared" si="54"/>
         <v>1904</v>
@@ -8104,7 +8116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <f t="shared" si="54"/>
         <v>1905</v>
@@ -8162,7 +8174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <f t="shared" si="54"/>
         <v>1906</v>
@@ -8220,7 +8232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <f t="shared" si="54"/>
         <v>1907</v>
@@ -8278,7 +8290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <f t="shared" si="54"/>
         <v>1908</v>
@@ -8325,7 +8337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <f t="shared" si="54"/>
         <v>1909</v>
@@ -8372,7 +8384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <f t="shared" si="54"/>
         <v>1910</v>
@@ -8419,7 +8431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <f t="shared" si="54"/>
         <v>1911</v>
@@ -8477,7 +8489,7 @@
         <v>15723.438359773389</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <f t="shared" si="54"/>
         <v>1912</v>
@@ -8524,7 +8536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <f t="shared" si="54"/>
         <v>1913</v>
@@ -8582,7 +8594,7 @@
         <v>36173.276557684701</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <f t="shared" si="54"/>
         <v>1914</v>
@@ -8629,7 +8641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <f t="shared" si="54"/>
         <v>1915</v>
@@ -8676,7 +8688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <f t="shared" si="54"/>
         <v>1916</v>
@@ -8723,7 +8735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>1917</v>
       </c>
@@ -8780,7 +8792,7 @@
         <v>639.69124188047317</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -8795,9 +8807,9 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="30" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -8812,7 +8824,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -8827,7 +8839,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>1911</v>
       </c>
@@ -8868,7 +8880,7 @@
         <v>-11.876056132993654</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <f>A142+1</f>
         <v>1912</v>
@@ -8886,7 +8898,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <f t="shared" ref="A144:A148" si="74">A143+1</f>
         <v>1913</v>
@@ -8928,7 +8940,7 @@
         <v>116.94950349421394</v>
       </c>
     </row>
-    <row r="145" spans="1:15">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <f t="shared" si="74"/>
         <v>1914</v>
@@ -8946,7 +8958,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:15">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <f t="shared" si="74"/>
         <v>1915</v>
@@ -8964,7 +8976,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:15">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <f t="shared" si="74"/>
         <v>1916</v>
@@ -8982,7 +8994,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:15">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <f t="shared" si="74"/>
         <v>1917</v>
@@ -9024,7 +9036,7 @@
         <v>218.84913831012869</v>
       </c>
     </row>
-    <row r="149" spans="1:15">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -9039,9 +9051,9 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:15">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="30" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -9056,7 +9068,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:15">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -9071,7 +9083,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:15">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="str">
         <f t="shared" ref="A152:M152" si="76">A116</f>
         <v>фин. год</v>
@@ -9130,7 +9142,7 @@
         <v>разница</v>
       </c>
     </row>
-    <row r="153" spans="1:15">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <f t="shared" ref="A153:M153" si="77">A117</f>
         <v>1896</v>
@@ -9189,7 +9201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <f t="shared" ref="A154:M154" si="79">A118</f>
         <v>1897</v>
@@ -9248,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <f t="shared" ref="A155:M155" si="80">A119</f>
         <v>1898</v>
@@ -9307,7 +9319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <f t="shared" ref="A156:M156" si="81">A120</f>
         <v>1899</v>
@@ -9366,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <f t="shared" ref="A157:M157" si="82">A121</f>
         <v>1900</v>
@@ -9425,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <f t="shared" ref="A158:M158" si="83">A122</f>
         <v>1901</v>
@@ -9484,7 +9496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <f t="shared" ref="A159:M159" si="84">A123</f>
         <v>1902</v>
@@ -9543,7 +9555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <f t="shared" ref="A160:M160" si="85">A124</f>
         <v>1903</v>
@@ -9602,7 +9614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <f t="shared" ref="A161:M161" si="86">A125</f>
         <v>1904</v>
@@ -9661,7 +9673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <f t="shared" ref="A162:M162" si="87">A126</f>
         <v>1905</v>
@@ -9720,7 +9732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <f t="shared" ref="A163:M163" si="88">A127</f>
         <v>1906</v>
@@ -9779,7 +9791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <f t="shared" ref="A164:M164" si="89">A128</f>
         <v>1907</v>
@@ -9838,7 +9850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <f t="shared" ref="A165:M165" si="90">A129</f>
         <v>1908</v>
@@ -9897,7 +9909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <f t="shared" ref="A166:M166" si="91">A130</f>
         <v>1909</v>
@@ -9956,7 +9968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <f t="shared" ref="A167:M167" si="92">A131</f>
         <v>1910</v>
@@ -10015,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <f t="shared" ref="A168:A174" si="93">A132</f>
         <v>1911</v>
@@ -10074,7 +10086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <f t="shared" si="93"/>
         <v>1912</v>
@@ -10133,7 +10145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <f t="shared" si="93"/>
         <v>1913</v>
@@ -10192,7 +10204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <f t="shared" si="93"/>
         <v>1914</v>
@@ -10251,7 +10263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <f t="shared" si="93"/>
         <v>1915</v>
@@ -10310,7 +10322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <f t="shared" si="93"/>
         <v>1916</v>
@@ -10369,7 +10381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <f t="shared" si="93"/>
         <v>1917</v>
@@ -10428,12 +10440,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="178" spans="1:16">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
         <v>84</v>
       </c>
@@ -10474,10 +10486,10 @@
         <v>81</v>
       </c>
       <c r="O178" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="179" spans="1:16">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>1896</v>
       </c>
@@ -10535,7 +10547,7 @@
       </c>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="1:16">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <f>A179+1</f>
         <v>1897</v>
@@ -10594,7 +10606,7 @@
       </c>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="1:16">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <f t="shared" ref="A181:A199" si="104">A180+1</f>
         <v>1898</v>
@@ -10653,7 +10665,7 @@
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <f t="shared" si="104"/>
         <v>1899</v>
@@ -10712,7 +10724,7 @@
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <f t="shared" si="104"/>
         <v>1900</v>
@@ -10771,7 +10783,7 @@
       </c>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="1:16">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <f t="shared" si="104"/>
         <v>1901</v>
@@ -10830,7 +10842,7 @@
       </c>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="1:16">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <f t="shared" si="104"/>
         <v>1902</v>
@@ -10889,7 +10901,7 @@
       </c>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="1:16">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <f t="shared" si="104"/>
         <v>1903</v>
@@ -10948,7 +10960,7 @@
       </c>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="1:16">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <f t="shared" si="104"/>
         <v>1904</v>
@@ -11007,7 +11019,7 @@
       </c>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="1:16">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <f t="shared" si="104"/>
         <v>1905</v>
@@ -11066,7 +11078,7 @@
       </c>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="1:16">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <f t="shared" si="104"/>
         <v>1906</v>
@@ -11125,7 +11137,7 @@
       </c>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="1:16">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <f t="shared" si="104"/>
         <v>1907</v>
@@ -11184,7 +11196,7 @@
       </c>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="1:16">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <f t="shared" si="104"/>
         <v>1908</v>
@@ -11242,7 +11254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:16">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <f t="shared" si="104"/>
         <v>1909</v>
@@ -11300,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <f t="shared" si="104"/>
         <v>1910</v>
@@ -11358,7 +11370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <f t="shared" si="104"/>
         <v>1911</v>
@@ -11416,7 +11428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <f t="shared" si="104"/>
         <v>1912</v>
@@ -11474,7 +11486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <f t="shared" si="104"/>
         <v>1913</v>
@@ -11532,7 +11544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:15">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <f t="shared" si="104"/>
         <v>1914</v>
@@ -11590,7 +11602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <f t="shared" si="104"/>
         <v>1915</v>
@@ -11648,7 +11660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <f t="shared" si="104"/>
         <v>1916</v>
@@ -11706,7 +11718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>1917</v>
       </c>
@@ -11763,12 +11775,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
         <v>87</v>
       </c>
@@ -11809,10 +11821,10 @@
         <v>81</v>
       </c>
       <c r="O204" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="205" spans="1:15">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>1896</v>
       </c>
@@ -11869,7 +11881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <f>A205+1</f>
         <v>1897</v>
@@ -11927,7 +11939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <f t="shared" ref="A207:A224" si="128">A206+1</f>
         <v>1898</v>
@@ -11985,7 +11997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <f t="shared" si="128"/>
         <v>1899</v>
@@ -12043,7 +12055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <f t="shared" si="128"/>
         <v>1900</v>
@@ -12101,7 +12113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <f t="shared" si="128"/>
         <v>1901</v>
@@ -12159,7 +12171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:15">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <f t="shared" si="128"/>
         <v>1902</v>
@@ -12217,7 +12229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <f t="shared" si="128"/>
         <v>1903</v>
@@ -12275,7 +12287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <f t="shared" si="128"/>
         <v>1904</v>
@@ -12333,7 +12345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <f t="shared" si="128"/>
         <v>1905</v>
@@ -12391,7 +12403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <f t="shared" si="128"/>
         <v>1906</v>
@@ -12449,7 +12461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15">
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <f t="shared" si="128"/>
         <v>1907</v>
@@ -12507,7 +12519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15">
+    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <f t="shared" si="128"/>
         <v>1908</v>
@@ -12565,7 +12577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15">
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <f t="shared" si="128"/>
         <v>1909</v>
@@ -12623,7 +12635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15">
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <f t="shared" si="128"/>
         <v>1910</v>
@@ -12681,7 +12693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15">
+    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <f t="shared" si="128"/>
         <v>1911</v>
@@ -12739,7 +12751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15">
+    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <f t="shared" si="128"/>
         <v>1912</v>
@@ -12797,7 +12809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15">
+    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <f t="shared" si="128"/>
         <v>1913</v>
@@ -12855,7 +12867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15">
+    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <f t="shared" si="128"/>
         <v>1914</v>
@@ -12913,7 +12925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15">
+    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <f t="shared" si="128"/>
         <v>1915</v>
@@ -12971,7 +12983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15">
+    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>1916</v>
       </c>
@@ -13028,7 +13040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15">
+    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A226" s="11" t="s">
         <v>49</v>
       </c>
@@ -13085,7 +13097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15">
+    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A227" s="11" t="s">
         <v>88</v>
       </c>
@@ -13138,27 +13150,27 @@
         <v>8.2845503895924058E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:15">
+    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="230" spans="1:15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L230" s="4"/>
     </row>
-    <row r="231" spans="1:15">
+    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G231">
         <v>89</v>
       </c>
       <c r="L231" s="4"/>
     </row>
-    <row r="232" spans="1:15">
+    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
       <c r="L232" s="4"/>
     </row>
-    <row r="233" spans="1:15">
+    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A233" s="10" t="s">
         <v>87</v>
       </c>
@@ -13199,10 +13211,10 @@
         <v>81</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="234" spans="1:15">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>1896</v>
       </c>
@@ -13259,7 +13271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15">
+    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <f>A234+1</f>
         <v>1897</v>
@@ -13317,7 +13329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15">
+    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <f t="shared" ref="A236:A253" si="153">A235+1</f>
         <v>1898</v>
@@ -13375,7 +13387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15">
+    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <f t="shared" si="153"/>
         <v>1899</v>
@@ -13433,7 +13445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15">
+    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <f t="shared" si="153"/>
         <v>1900</v>
@@ -13491,7 +13503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15">
+    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <f t="shared" si="153"/>
         <v>1901</v>
@@ -13549,7 +13561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15">
+    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <f t="shared" si="153"/>
         <v>1902</v>
@@ -13607,7 +13619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15">
+    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <f t="shared" si="153"/>
         <v>1903</v>
@@ -13665,7 +13677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15">
+    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <f t="shared" si="153"/>
         <v>1904</v>
@@ -13723,7 +13735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15">
+    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <f t="shared" si="153"/>
         <v>1905</v>
@@ -13781,7 +13793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15">
+    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <f t="shared" si="153"/>
         <v>1906</v>
@@ -13839,7 +13851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15">
+    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <f t="shared" si="153"/>
         <v>1907</v>
@@ -13897,7 +13909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15">
+    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <f t="shared" si="153"/>
         <v>1908</v>
@@ -13955,7 +13967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15">
+    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <f t="shared" si="153"/>
         <v>1909</v>
@@ -14013,7 +14025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15">
+    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <f t="shared" si="153"/>
         <v>1910</v>
@@ -14071,7 +14083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15">
+    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <f t="shared" si="153"/>
         <v>1911</v>
@@ -14129,7 +14141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15">
+    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <f t="shared" si="153"/>
         <v>1912</v>
@@ -14187,7 +14199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15">
+    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <f t="shared" si="153"/>
         <v>1913</v>
@@ -14245,7 +14257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15">
+    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <f t="shared" si="153"/>
         <v>1914</v>
@@ -14303,7 +14315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15">
+    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <f t="shared" si="153"/>
         <v>1915</v>
@@ -14361,7 +14373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15">
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>1916</v>
       </c>
@@ -14418,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15">
+    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A255" s="11" t="s">
         <v>49</v>
       </c>
@@ -14475,14 +14487,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="259" spans="1:17">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A259" s="14" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B259" s="10" t="s">
         <v>70</v>
@@ -14521,7 +14533,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="1:17">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B260">
         <v>0.55000000000000004</v>
       </c>
@@ -14556,7 +14568,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="262" spans="1:17">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
         <v>87</v>
       </c>
@@ -14597,10 +14609,10 @@
         <v>81</v>
       </c>
       <c r="O262" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="263" spans="1:17">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>1896</v>
       </c>
@@ -14657,7 +14669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <f>A263+1</f>
         <v>1897</v>
@@ -14715,7 +14727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <f t="shared" ref="A265:A282" si="179">A264+1</f>
         <v>1898</v>
@@ -14773,7 +14785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <f t="shared" si="179"/>
         <v>1899</v>
@@ -14831,7 +14843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <f t="shared" si="179"/>
         <v>1900</v>
@@ -14889,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <f t="shared" si="179"/>
         <v>1901</v>
@@ -14948,7 +14960,7 @@
       </c>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="1:17">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <f t="shared" si="179"/>
         <v>1902</v>
@@ -15006,7 +15018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <f t="shared" si="179"/>
         <v>1903</v>
@@ -15064,7 +15076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <f t="shared" si="179"/>
         <v>1904</v>
@@ -15122,7 +15134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <f t="shared" si="179"/>
         <v>1905</v>
@@ -15180,7 +15192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:15">
+    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <f t="shared" si="179"/>
         <v>1906</v>
@@ -15238,7 +15250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15">
+    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <f t="shared" si="179"/>
         <v>1907</v>
@@ -15296,7 +15308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15">
+    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <f t="shared" si="179"/>
         <v>1908</v>
@@ -15354,7 +15366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15">
+    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <f t="shared" si="179"/>
         <v>1909</v>
@@ -15412,7 +15424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15">
+    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <f t="shared" si="179"/>
         <v>1910</v>
@@ -15470,7 +15482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15">
+    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <f t="shared" si="179"/>
         <v>1911</v>
@@ -15528,7 +15540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15">
+    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <f t="shared" si="179"/>
         <v>1912</v>
@@ -15586,7 +15598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15">
+    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <f t="shared" si="179"/>
         <v>1913</v>
@@ -15644,7 +15656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15">
+    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <f t="shared" si="179"/>
         <v>1914</v>
@@ -15702,7 +15714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15">
+    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <f t="shared" si="179"/>
         <v>1915</v>
@@ -15760,7 +15772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15">
+    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>1916</v>
       </c>
@@ -15817,7 +15829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15">
+    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" s="11" t="s">
         <v>49</v>
       </c>
@@ -15874,12 +15886,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15">
+    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="288" spans="1:15">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
         <v>87</v>
       </c>
@@ -15920,10 +15932,10 @@
         <v>81</v>
       </c>
       <c r="O288" s="10" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="289" spans="1:15">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>1896</v>
       </c>
@@ -15980,7 +15992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:15">
+    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <f>A289+1</f>
         <v>1897</v>
@@ -16038,7 +16050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15">
+    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <f t="shared" ref="A291:A308" si="203">A290+1</f>
         <v>1898</v>
@@ -16096,7 +16108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:15">
+    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <f t="shared" si="203"/>
         <v>1899</v>
@@ -16154,7 +16166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15">
+    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <f t="shared" si="203"/>
         <v>1900</v>
@@ -16212,7 +16224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15">
+    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <f t="shared" si="203"/>
         <v>1901</v>
@@ -16270,7 +16282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15">
+    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <f t="shared" si="203"/>
         <v>1902</v>
@@ -16328,7 +16340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15">
+    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <f t="shared" si="203"/>
         <v>1903</v>
@@ -16386,7 +16398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15">
+    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <f t="shared" si="203"/>
         <v>1904</v>
@@ -16444,7 +16456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15">
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <f t="shared" si="203"/>
         <v>1905</v>
@@ -16502,7 +16514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15">
+    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <f t="shared" si="203"/>
         <v>1906</v>
@@ -16560,7 +16572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15">
+    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <f t="shared" si="203"/>
         <v>1907</v>
@@ -16618,7 +16630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15">
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <f t="shared" si="203"/>
         <v>1908</v>
@@ -16676,7 +16688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15">
+    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <f t="shared" si="203"/>
         <v>1909</v>
@@ -16734,7 +16746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15">
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <f t="shared" si="203"/>
         <v>1910</v>
@@ -16792,7 +16804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15">
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <f t="shared" si="203"/>
         <v>1911</v>
@@ -16850,7 +16862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15">
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <f t="shared" si="203"/>
         <v>1912</v>
@@ -16908,7 +16920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15">
+    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <f t="shared" si="203"/>
         <v>1913</v>
@@ -16966,7 +16978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15">
+    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <f t="shared" si="203"/>
         <v>1914</v>
@@ -17024,7 +17036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15">
+    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <f t="shared" si="203"/>
         <v>1915</v>
@@ -17082,7 +17094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15">
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>1916</v>
       </c>
@@ -17139,7 +17151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15">
+    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A310" s="11" t="s">
         <v>49</v>
       </c>
@@ -17207,26 +17219,27 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
-  <dimension ref="A1:P82"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:P99"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.41796875" customWidth="1"/>
-    <col min="2" max="2" width="17.41796875" customWidth="1"/>
-    <col min="3" max="3" width="10.68359375" customWidth="1"/>
-    <col min="4" max="4" width="14.3125" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="57.6">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -17261,7 +17274,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -17298,7 +17311,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -17335,7 +17348,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -17372,7 +17385,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -17409,7 +17422,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -17446,7 +17459,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -17483,7 +17496,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -17520,7 +17533,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -17557,7 +17570,7 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -17594,7 +17607,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -17641,7 +17654,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
@@ -17687,7 +17700,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>127</v>
       </c>
@@ -17732,7 +17745,7 @@
         <v>1395970</v>
       </c>
     </row>
-    <row r="17" spans="1:16">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>128</v>
       </c>
@@ -17777,99 +17790,99 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="B18" s="35">
-        <f>SUM(B7:B9)</f>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A18" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="B18" s="34">
+        <f t="shared" ref="B18:K18" si="12">SUM(B7:B9)</f>
         <v>9362</v>
       </c>
-      <c r="C18" s="35">
-        <f>SUM(C7:C9)</f>
+      <c r="C18" s="34">
+        <f t="shared" si="12"/>
         <v>504007</v>
       </c>
-      <c r="D18" s="35">
-        <f>SUM(D7:D9)</f>
+      <c r="D18" s="34">
+        <f t="shared" si="12"/>
         <v>9713</v>
       </c>
-      <c r="E18" s="35">
-        <f>SUM(E7:E9)</f>
+      <c r="E18" s="34">
+        <f t="shared" si="12"/>
         <v>40349</v>
       </c>
-      <c r="F18" s="35">
-        <f>SUM(F7:F9)</f>
+      <c r="F18" s="34">
+        <f t="shared" si="12"/>
         <v>92</v>
       </c>
-      <c r="G18" s="35">
-        <f>SUM(G7:G9)</f>
+      <c r="G18" s="34">
+        <f t="shared" si="12"/>
         <v>49</v>
       </c>
-      <c r="H18" s="35">
-        <f>SUM(H7:H9)</f>
+      <c r="H18" s="34">
+        <f t="shared" si="12"/>
         <v>368</v>
       </c>
-      <c r="I18" s="35">
-        <f>SUM(I7:I9)</f>
+      <c r="I18" s="34">
+        <f t="shared" si="12"/>
         <v>2958</v>
       </c>
-      <c r="J18" s="35">
-        <f>SUM(J7:J9)</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="35">
-        <f>SUM(K7:K9)</f>
+      <c r="J18" s="34">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="34">
+        <f t="shared" si="12"/>
         <v>566899</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="B19" s="36">
-        <f>B18/$K18*100</f>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B19" s="35">
+        <f t="shared" ref="B19:K19" si="13">B18/$K18*100</f>
         <v>1.6514405564306869</v>
       </c>
-      <c r="C19" s="36">
-        <f>C18/$K18*100</f>
+      <c r="C19" s="35">
+        <f t="shared" si="13"/>
         <v>88.905960320974287</v>
       </c>
-      <c r="D19" s="36">
-        <f>D18/$K18*100</f>
+      <c r="D19" s="35">
+        <f t="shared" si="13"/>
         <v>1.7133563474269666</v>
       </c>
-      <c r="E19" s="36">
-        <f>E18/$K18*100</f>
+      <c r="E19" s="35">
+        <f t="shared" si="13"/>
         <v>7.1174935923330258</v>
       </c>
-      <c r="F19" s="36">
-        <f>F18/$K18*100</f>
+      <c r="F19" s="35">
+        <f t="shared" si="13"/>
         <v>1.6228640375093271E-2</v>
       </c>
-      <c r="G19" s="36">
-        <f>G18/$K18*100</f>
+      <c r="G19" s="35">
+        <f t="shared" si="13"/>
         <v>8.6435149823866336E-3</v>
       </c>
-      <c r="H19" s="36">
-        <f>H18/$K18*100</f>
+      <c r="H19" s="35">
+        <f t="shared" si="13"/>
         <v>6.4914561500373086E-2</v>
       </c>
-      <c r="I19" s="36">
-        <f>I18/$K18*100</f>
+      <c r="I19" s="35">
+        <f t="shared" si="13"/>
         <v>0.52178606771223801</v>
       </c>
-      <c r="J19" s="36">
-        <f>J18/$K18*100</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="36">
-        <f>K18/$K18*100</f>
+      <c r="J19" s="35">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="35">
+        <f t="shared" si="13"/>
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:16">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -17882,9 +17895,9 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:16">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -17897,7 +17910,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:16">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -17909,38 +17922,38 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="37" t="s">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>117</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="37" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="G25" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="C25" s="38" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" s="38" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="38" t="s">
-        <v>111</v>
-      </c>
-      <c r="F25" s="38" t="s">
+      <c r="H25" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="G25" s="38" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="I25" s="38" t="s">
+      <c r="I25" s="37" t="s">
         <v>80</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:16">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -17964,7 +17977,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -17990,7 +18003,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:16">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -18002,7 +18015,7 @@
         <v>4035</v>
       </c>
       <c r="E28" s="4">
-        <v>27261</v>
+        <v>27271</v>
       </c>
       <c r="F28" s="4">
         <v>5</v>
@@ -18011,12 +18024,12 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4">
         <f>SUM(B28:H28)</f>
-        <v>173846</v>
+        <v>173856</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:16">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>122</v>
       </c>
@@ -18042,7 +18055,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:16">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
         <v>123</v>
       </c>
@@ -18073,7 +18086,7 @@
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
     </row>
-    <row r="31" spans="1:16">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -18097,7 +18110,7 @@
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="4">
-        <f t="shared" ref="I31:I36" si="12">SUM(B31:H31)</f>
+        <f t="shared" ref="I31:I36" si="14">SUM(B31:H31)</f>
         <v>713875</v>
       </c>
       <c r="J31" s="4"/>
@@ -18108,7 +18121,7 @@
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
     </row>
-    <row r="32" spans="1:16">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -18130,7 +18143,7 @@
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1047253</v>
       </c>
       <c r="J32" s="4"/>
@@ -18141,7 +18154,7 @@
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
     </row>
-    <row r="33" spans="1:16">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -18165,7 +18178,7 @@
         <v>404</v>
       </c>
       <c r="I33" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>1048709</v>
       </c>
       <c r="J33" s="4"/>
@@ -18176,7 +18189,7 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="27" t="s">
         <v>127</v>
       </c>
@@ -18185,31 +18198,31 @@
         <v>97622</v>
       </c>
       <c r="C34" s="12">
-        <f t="shared" ref="C34:H34" si="13">SUM(C30:C33)</f>
+        <f t="shared" ref="C34:H34" si="15">SUM(C30:C33)</f>
         <v>2770167</v>
       </c>
       <c r="D34" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>146257</v>
       </c>
       <c r="E34" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>54254</v>
       </c>
       <c r="F34" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>27</v>
       </c>
       <c r="G34" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>8407</v>
       </c>
       <c r="H34" s="12">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>404</v>
       </c>
       <c r="I34" s="12">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3077138</v>
       </c>
       <c r="J34" s="4"/>
@@ -18220,7 +18233,7 @@
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
     </row>
-    <row r="35" spans="1:16">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="22" t="s">
         <v>88</v>
       </c>
@@ -18229,31 +18242,31 @@
         <v>3.1724934013359167</v>
       </c>
       <c r="C35" s="23">
-        <f t="shared" ref="C35:I35" si="14">100*C34/$I34</f>
+        <f t="shared" ref="C35:I35" si="16">100*C34/$I34</f>
         <v>90.024139313868929</v>
       </c>
       <c r="D35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>4.7530205015179687</v>
       </c>
       <c r="E35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.76313184524061</v>
       </c>
       <c r="F35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>8.7743871090604326E-4</v>
       </c>
       <c r="G35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>0.27320841639211502</v>
       </c>
       <c r="H35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>1.3129082933557091E-2</v>
       </c>
       <c r="I35" s="23">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v>100</v>
       </c>
       <c r="J35" s="4"/>
@@ -18264,32 +18277,32 @@
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
     </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="B36" s="35"/>
-      <c r="C36" s="35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34">
         <f>SUM(C27:C29)</f>
         <v>447806</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="34">
         <f>SUM(D27:D29)</f>
         <v>15165</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="34">
         <f>SUM(E27:E29)</f>
-        <v>40789</v>
-      </c>
-      <c r="F36" s="35">
+        <v>40799</v>
+      </c>
+      <c r="F36" s="34">
         <f>SUM(F27:F29)</f>
         <v>35</v>
       </c>
-      <c r="G36" s="35"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35">
-        <f t="shared" si="12"/>
-        <v>503795</v>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34">
+        <f t="shared" si="14"/>
+        <v>503805</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
@@ -18299,433 +18312,851 @@
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
     </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="34" t="s">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="B37" s="36"/>
-      <c r="C37" s="36">
+      <c r="B37" s="35"/>
+      <c r="C37" s="35">
         <f>C36/$I36*100</f>
-        <v>88.886551077323119</v>
-      </c>
-      <c r="D37" s="36">
+        <v>88.88478677266005</v>
+      </c>
+      <c r="D37" s="35">
         <f>D36/$I36*100</f>
-        <v>3.0101529391915363</v>
-      </c>
-      <c r="E37" s="36">
+        <v>3.0100931908178761</v>
+      </c>
+      <c r="E37" s="35">
         <f>E36/$I36*100</f>
-        <v>8.096348713266309</v>
-      </c>
-      <c r="F37" s="36"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="36">
+        <v>8.0981729041990462</v>
+      </c>
+      <c r="F37" s="35"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="35">
         <f>SUM(B37:H37)</f>
-        <v>99.99305272978097</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16">
+        <v>99.993052867676965</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="37" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>111</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="40" t="s">
+        <v>150</v>
+      </c>
+      <c r="H42" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="J42" s="40" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4">
+        <v>23669</v>
+      </c>
+      <c r="D43" s="4">
+        <v>190</v>
+      </c>
+      <c r="E43" s="4">
+        <v>7463</v>
+      </c>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+      <c r="H43" s="4"/>
+      <c r="I43" s="4">
+        <v>2336</v>
+      </c>
+      <c r="J43" s="4">
+        <f>SUM(B43:I43)</f>
+        <v>33658</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4">
+        <v>58829</v>
+      </c>
+      <c r="D44" s="4">
+        <v>120</v>
+      </c>
+      <c r="E44" s="4">
+        <v>1066</v>
+      </c>
+      <c r="F44" s="4">
+        <v>8</v>
+      </c>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4">
+        <v>9959</v>
+      </c>
+      <c r="J44" s="4">
+        <f t="shared" ref="J44:J51" si="17">SUM(B44:I44)</f>
+        <v>69982</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4">
+        <v>142545</v>
+      </c>
+      <c r="D45" s="4">
+        <v>4035</v>
+      </c>
+      <c r="E45" s="4">
+        <v>27271</v>
+      </c>
+      <c r="F45" s="4">
+        <v>5</v>
+      </c>
+      <c r="G45" s="4"/>
+      <c r="H45" s="4"/>
+      <c r="I45" s="4">
+        <v>15994</v>
+      </c>
+      <c r="J45" s="4">
+        <f t="shared" si="17"/>
+        <v>189850</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>122</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4">
+        <v>246432</v>
+      </c>
+      <c r="D46" s="4">
+        <v>11010</v>
+      </c>
+      <c r="E46" s="4">
+        <v>12462</v>
+      </c>
+      <c r="F46" s="4">
+        <v>22</v>
+      </c>
+      <c r="G46" s="4"/>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4">
+        <v>44935</v>
+      </c>
+      <c r="J46" s="4">
+        <f t="shared" si="17"/>
+        <v>314861</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
+        <v>123</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4">
+        <v>258858</v>
+      </c>
+      <c r="D47" s="4">
+        <v>6456</v>
+      </c>
+      <c r="E47" s="4">
+        <v>1978</v>
+      </c>
+      <c r="F47" s="4">
+        <v>9</v>
+      </c>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4">
+        <v>9582</v>
+      </c>
+      <c r="J47" s="4">
+        <f t="shared" si="17"/>
+        <v>276883</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="4">
+        <v>12995</v>
+      </c>
+      <c r="C48" s="4">
+        <v>678735</v>
+      </c>
+      <c r="D48" s="4">
+        <v>19739</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1861</v>
+      </c>
+      <c r="F48" s="4">
+        <v>18</v>
+      </c>
+      <c r="G48" s="4">
+        <v>527</v>
+      </c>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4">
+        <f t="shared" si="17"/>
+        <v>713875</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>125</v>
+      </c>
+      <c r="B49" s="4">
+        <v>26337</v>
+      </c>
+      <c r="C49" s="4">
+        <v>938571</v>
+      </c>
+      <c r="D49" s="4">
+        <v>64754</v>
+      </c>
+      <c r="E49" s="4">
+        <v>15360</v>
+      </c>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4">
+        <v>2231</v>
+      </c>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4">
+        <f t="shared" si="17"/>
+        <v>1047253</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="4">
+        <v>58290</v>
+      </c>
+      <c r="C50" s="4">
+        <v>894003</v>
+      </c>
+      <c r="D50" s="4">
+        <v>55308</v>
+      </c>
+      <c r="E50" s="4">
+        <v>35055</v>
+      </c>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4">
+        <v>5649</v>
+      </c>
+      <c r="H50" s="4">
+        <v>404</v>
+      </c>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4">
+        <f t="shared" si="17"/>
+        <v>1048709</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="12">
+        <f>SUM(B47:B50)</f>
+        <v>97622</v>
+      </c>
+      <c r="C51" s="12">
+        <f t="shared" ref="C51:I51" si="18">SUM(C47:C50)</f>
+        <v>2770167</v>
+      </c>
+      <c r="D51" s="12">
+        <f t="shared" si="18"/>
+        <v>146257</v>
+      </c>
+      <c r="E51" s="12">
+        <f t="shared" si="18"/>
+        <v>54254</v>
+      </c>
+      <c r="F51" s="12">
+        <f t="shared" si="18"/>
+        <v>27</v>
+      </c>
+      <c r="G51" s="12">
+        <f t="shared" si="18"/>
+        <v>8407</v>
+      </c>
+      <c r="H51" s="12">
+        <f t="shared" si="18"/>
+        <v>404</v>
+      </c>
+      <c r="I51" s="12">
+        <f t="shared" si="18"/>
+        <v>9582</v>
+      </c>
+      <c r="J51" s="12">
+        <f t="shared" si="17"/>
+        <v>3086720</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B52" s="23">
+        <f>100*B51/$J51</f>
+        <v>3.162645137880987</v>
+      </c>
+      <c r="C52" s="23">
+        <f>100*C51/$J51</f>
+        <v>89.744680437487048</v>
+      </c>
+      <c r="D52" s="23">
+        <f>100*D51/$J51</f>
+        <v>4.7382658614969939</v>
+      </c>
+      <c r="E52" s="23">
+        <f>100*E51/$J51</f>
+        <v>1.7576586149699358</v>
+      </c>
+      <c r="F52" s="23">
+        <f>100*F51/$J51</f>
+        <v>8.7471490773377569E-4</v>
+      </c>
+      <c r="G52" s="23">
+        <f>100*G51/$J51</f>
+        <v>0.27236030478955009</v>
+      </c>
+      <c r="H52" s="23">
+        <f>100*H51/$J51</f>
+        <v>1.308832676757205E-2</v>
+      </c>
+      <c r="I52" s="23">
+        <f>100*I51/$J51</f>
+        <v>0.3104266017001866</v>
+      </c>
+      <c r="J52" s="23">
+        <f>100*J51/$J51</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34">
+        <f>SUM(C44:C46)</f>
+        <v>447806</v>
+      </c>
+      <c r="D53" s="34">
+        <f>SUM(D44:D46)</f>
+        <v>15165</v>
+      </c>
+      <c r="E53" s="34">
+        <f>SUM(E44:E46)</f>
+        <v>40799</v>
+      </c>
+      <c r="F53" s="34">
+        <f>SUM(F44:F46)</f>
+        <v>35</v>
+      </c>
+      <c r="G53" s="34">
+        <f>SUM(G44:G46)</f>
+        <v>0</v>
+      </c>
+      <c r="H53" s="34">
+        <f>SUM(H44:H46)</f>
+        <v>0</v>
+      </c>
+      <c r="I53" s="34">
+        <f>SUM(I44:I46)</f>
+        <v>70888</v>
+      </c>
+      <c r="J53" s="34">
+        <f>SUM(B53:I53)</f>
+        <v>574693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="35"/>
+      <c r="C54" s="35">
+        <f>C53/$J53*100</f>
+        <v>77.920907336612771</v>
+      </c>
+      <c r="D54" s="35">
+        <f>D53/$J53*100</f>
+        <v>2.6388001941906372</v>
+      </c>
+      <c r="E54" s="35">
+        <f>E53/$J53*100</f>
+        <v>7.099268653002559</v>
+      </c>
+      <c r="F54" s="35">
+        <f>F53/$J53*100</f>
+        <v>6.0902081633150218E-3</v>
+      </c>
+      <c r="G54" s="35">
+        <f>G53/$J53*100</f>
+        <v>0</v>
+      </c>
+      <c r="H54" s="35">
+        <f>H53/$J53*100</f>
+        <v>0</v>
+      </c>
+      <c r="I54" s="35">
+        <f>I53/$J53*100</f>
+        <v>12.334933608030722</v>
+      </c>
+      <c r="J54" s="35">
+        <f>SUM(B54:H54)</f>
+        <v>87.665066391969276</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="37" t="s">
+      <c r="B59" s="36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>1896</v>
+      </c>
+      <c r="B60" s="4">
+        <v>35639</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>1897</v>
+      </c>
+      <c r="B61" s="4">
+        <v>28021</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>1898</v>
+      </c>
+      <c r="B62" s="4">
+        <v>41907</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>1899</v>
+      </c>
+      <c r="B63" s="4">
+        <v>65559</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>1900</v>
+      </c>
+      <c r="B64" s="4">
+        <v>76085</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>1901</v>
+      </c>
+      <c r="B65" s="4">
+        <v>83166</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>1902</v>
+      </c>
+      <c r="B66" s="4">
+        <v>103114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>1903</v>
+      </c>
+      <c r="B67" s="4">
+        <v>125022</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>1904</v>
+      </c>
+      <c r="B68" s="4">
+        <v>151739</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1905</v>
+      </c>
+      <c r="B69" s="4">
+        <v>186157</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1906</v>
+      </c>
+      <c r="B70" s="4">
+        <v>221400</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>1907</v>
+      </c>
+      <c r="B71" s="4">
+        <v>186071</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>1908</v>
+      </c>
+      <c r="B72" s="4">
+        <v>119541</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>1909</v>
+      </c>
+      <c r="B73" s="4">
+        <v>141698</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>1910</v>
+      </c>
+      <c r="B74" s="4">
+        <v>162676</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>1911</v>
+      </c>
+      <c r="B75" s="4">
+        <v>144660</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>1912</v>
+      </c>
+      <c r="B76" s="4">
+        <v>217990</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>1913</v>
+      </c>
+      <c r="B77" s="4">
+        <v>261265</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>1914</v>
+      </c>
+      <c r="B78" s="4">
+        <v>119358</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>1915</v>
+      </c>
+      <c r="B79" s="4">
+        <v>3880</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>1916</v>
+      </c>
+      <c r="B80" s="4">
+        <v>2305</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>49</v>
+      </c>
+      <c r="B81" s="4">
+        <f>SUM(B60:B80)</f>
+        <v>2477253</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>123</v>
+      </c>
+      <c r="B82" s="4">
+        <f>SUM(B60:B64)</f>
+        <v>247211</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>124</v>
+      </c>
+      <c r="B83" s="4">
+        <f>SUM(B65:B69)</f>
+        <v>649198</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>125</v>
+      </c>
+      <c r="B84" s="4">
+        <f>SUM(B70:B74)</f>
+        <v>831386</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>126</v>
+      </c>
+      <c r="B85" s="4">
+        <f>SUM(B75:B79)</f>
+        <v>747153</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B89" s="36" t="s">
+        <v>188</v>
+      </c>
+      <c r="C89" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="E89" s="36" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43">
-        <v>1896</v>
-      </c>
-      <c r="B43" s="4">
-        <v>35639</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44">
-        <v>1897</v>
-      </c>
-      <c r="B44" s="4">
-        <v>28021</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45">
-        <v>1898</v>
-      </c>
-      <c r="B45" s="4">
-        <v>41907</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46">
-        <v>1899</v>
-      </c>
-      <c r="B46" s="4">
-        <v>65559</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47">
-        <v>1900</v>
-      </c>
-      <c r="B47" s="4">
-        <v>76085</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48">
-        <v>1901</v>
-      </c>
-      <c r="B48" s="4">
-        <v>83166</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>1902</v>
-      </c>
-      <c r="B49" s="4">
-        <v>103114</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>1903</v>
-      </c>
-      <c r="B50" s="4">
-        <v>125022</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>1904</v>
-      </c>
-      <c r="B51" s="4">
-        <v>151739</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>1905</v>
-      </c>
-      <c r="B52" s="4">
-        <v>186157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>1906</v>
-      </c>
-      <c r="B53" s="4">
-        <v>221400</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>1907</v>
-      </c>
-      <c r="B54" s="4">
-        <v>186071</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>1908</v>
-      </c>
-      <c r="B55" s="4">
-        <v>119541</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>1909</v>
-      </c>
-      <c r="B56" s="4">
-        <v>141698</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>1910</v>
-      </c>
-      <c r="B57" s="4">
-        <v>162676</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>1911</v>
-      </c>
-      <c r="B58" s="4">
-        <v>144660</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>1912</v>
-      </c>
-      <c r="B59" s="4">
-        <v>217990</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>1913</v>
-      </c>
-      <c r="B60" s="4">
-        <v>261265</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
-        <v>1914</v>
-      </c>
-      <c r="B61" s="4">
-        <v>119358</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
-        <v>1915</v>
-      </c>
-      <c r="B62" s="4">
-        <v>3880</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
-        <v>1916</v>
-      </c>
-      <c r="B63" s="4">
-        <v>2305</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>49</v>
-      </c>
-      <c r="B64" s="4">
-        <f>SUM(B43:B63)</f>
-        <v>2477253</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" t="s">
-        <v>123</v>
-      </c>
-      <c r="B65" s="4">
-        <f>SUM(B43:B47)</f>
-        <v>247211</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" t="s">
-        <v>124</v>
-      </c>
-      <c r="B66" s="4">
-        <f>SUM(B48:B52)</f>
-        <v>649198</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" t="s">
-        <v>125</v>
-      </c>
-      <c r="B67" s="4">
-        <f>SUM(B53:B57)</f>
-        <v>831386</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68" t="s">
-        <v>126</v>
-      </c>
-      <c r="B68" s="4">
-        <f>SUM(B58:B62)</f>
-        <v>747153</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="B72" s="37" t="s">
-        <v>190</v>
-      </c>
-      <c r="C72" s="37" t="s">
-        <v>189</v>
-      </c>
-      <c r="D72" s="37" t="s">
-        <v>191</v>
-      </c>
-      <c r="E72" s="37" t="s">
-        <v>194</v>
-      </c>
-      <c r="F72" s="39"/>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73" t="s">
+      <c r="F89" s="38"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
         <v>119</v>
       </c>
-      <c r="B73" s="4">
+      <c r="B90" s="4">
         <f>K6</f>
         <v>27525</v>
       </c>
-      <c r="C73" s="4">
-        <f>I26</f>
-        <v>31322</v>
-      </c>
-      <c r="D73" s="26">
-        <f>B73/C73*100</f>
-        <v>87.877530170487191</v>
-      </c>
-      <c r="E73" s="14"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74" t="s">
+      <c r="C90" s="4">
+        <f>J43</f>
+        <v>33658</v>
+      </c>
+      <c r="D90" s="26">
+        <f>B90/C90*100</f>
+        <v>81.778477627904209</v>
+      </c>
+      <c r="E90" s="14"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
         <v>120</v>
       </c>
-      <c r="B74" s="4">
-        <f t="shared" ref="B74:B80" si="15">K7</f>
+      <c r="B91" s="4">
+        <f>K7</f>
         <v>64393</v>
       </c>
-      <c r="C74" s="4">
-        <f t="shared" ref="C74:C80" si="16">I27</f>
-        <v>60023</v>
-      </c>
-      <c r="D74" s="26">
-        <f>B74/C74*100</f>
-        <v>107.28054245872416</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75" t="s">
+      <c r="C91" s="4">
+        <f t="shared" ref="C91:C97" si="19">J44</f>
+        <v>69982</v>
+      </c>
+      <c r="D91" s="26">
+        <f>B91/C91*100</f>
+        <v>92.01366065559715</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
         <v>121</v>
       </c>
-      <c r="B75" s="4">
-        <f t="shared" si="15"/>
+      <c r="B92" s="4">
+        <f>K8</f>
         <v>223248</v>
       </c>
-      <c r="C75" s="4">
-        <f t="shared" si="16"/>
-        <v>173846</v>
-      </c>
-      <c r="D75" s="26">
-        <f t="shared" ref="D75:D80" si="17">B75/C75*100</f>
-        <v>128.41710479389806</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76" t="s">
+      <c r="C92" s="4">
+        <f t="shared" si="19"/>
+        <v>189850</v>
+      </c>
+      <c r="D92" s="26">
+        <f t="shared" ref="D92:D97" si="20">B92/C92*100</f>
+        <v>117.59178298656833</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
         <v>122</v>
       </c>
-      <c r="B76" s="4">
-        <f t="shared" si="15"/>
+      <c r="B93" s="4">
+        <f>K9</f>
         <v>279258</v>
       </c>
-      <c r="C76" s="4">
-        <f t="shared" si="16"/>
-        <v>269926</v>
-      </c>
-      <c r="D76" s="26">
-        <f t="shared" si="17"/>
-        <v>103.45724383719983</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77" s="21" t="s">
+      <c r="C93" s="4">
+        <f t="shared" si="19"/>
+        <v>314861</v>
+      </c>
+      <c r="D93" s="26">
+        <f t="shared" si="20"/>
+        <v>88.692470645777021</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B77" s="4">
-        <f t="shared" si="15"/>
+      <c r="B94" s="4">
+        <f>K10</f>
         <v>173914</v>
       </c>
-      <c r="C77" s="4">
-        <f t="shared" si="16"/>
-        <v>267301</v>
-      </c>
-      <c r="D77" s="26">
-        <f t="shared" si="17"/>
-        <v>65.062981432916445</v>
-      </c>
-      <c r="E77" s="4">
-        <f>B65</f>
+      <c r="C94" s="4">
+        <f t="shared" si="19"/>
+        <v>276883</v>
+      </c>
+      <c r="D94" s="26">
+        <f t="shared" si="20"/>
+        <v>62.811367978532452</v>
+      </c>
+      <c r="E94" s="4">
+        <f>B82</f>
         <v>247211</v>
       </c>
     </row>
-    <row r="78" spans="1:6">
-      <c r="A78" t="s">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
         <v>124</v>
       </c>
-      <c r="B78" s="4">
-        <f t="shared" si="15"/>
+      <c r="B95" s="4">
+        <f>K11</f>
         <v>340174</v>
       </c>
-      <c r="C78" s="4">
-        <f t="shared" si="16"/>
+      <c r="C95" s="4">
+        <f t="shared" si="19"/>
         <v>713875</v>
       </c>
-      <c r="D78" s="26">
-        <f t="shared" si="17"/>
+      <c r="D95" s="26">
+        <f t="shared" si="20"/>
         <v>47.651759761863069</v>
       </c>
-      <c r="E78" s="4">
-        <f>B66</f>
+      <c r="E95" s="4">
+        <f>B83</f>
         <v>649198</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
-      <c r="A79" t="s">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
         <v>125</v>
       </c>
-      <c r="B79" s="4">
-        <f t="shared" si="15"/>
+      <c r="B96" s="4">
+        <f>K12</f>
         <v>471971</v>
       </c>
-      <c r="C79" s="4">
-        <f t="shared" si="16"/>
+      <c r="C96" s="4">
+        <f t="shared" si="19"/>
         <v>1047253</v>
       </c>
-      <c r="D79" s="26">
-        <f t="shared" si="17"/>
+      <c r="D96" s="26">
+        <f t="shared" si="20"/>
         <v>45.067524275413867</v>
       </c>
-      <c r="E79" s="4">
-        <f>B67</f>
+      <c r="E96" s="4">
+        <f>B84</f>
         <v>831386</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
-      <c r="A80" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
         <v>126</v>
       </c>
-      <c r="B80" s="4">
-        <f t="shared" si="15"/>
+      <c r="B97" s="4">
+        <f>K13</f>
         <v>409911</v>
       </c>
-      <c r="C80" s="4">
-        <f t="shared" si="16"/>
+      <c r="C97" s="4">
+        <f t="shared" si="19"/>
         <v>1048709</v>
       </c>
-      <c r="D80" s="26">
-        <f t="shared" si="17"/>
+      <c r="D97" s="26">
+        <f t="shared" si="20"/>
         <v>39.087201502037267</v>
       </c>
-      <c r="E80" s="4">
-        <f>B68</f>
+      <c r="E97" s="4">
+        <f>B85</f>
         <v>747153</v>
       </c>
     </row>
-    <row r="81" spans="2:2">
-      <c r="B81" s="4"/>
-    </row>
-    <row r="82" spans="2:2">
-      <c r="B82" s="4"/>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="4"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B99" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18736,66 +19167,66 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.68359375" customWidth="1"/>
-    <col min="3" max="3" width="18.83984375" customWidth="1"/>
-    <col min="4" max="4" width="13.83984375" customWidth="1"/>
-    <col min="5" max="5" width="16.83984375" customWidth="1"/>
-    <col min="7" max="7" width="13.26171875" customWidth="1"/>
-    <col min="8" max="8" width="16.41796875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="B5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="B6" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>1908</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="1">
         <v>1917</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
         <v>1918</v>
       </c>
@@ -18803,47 +19234,47 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="33"/>
-      <c r="G14" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="H14" s="33"/>
-    </row>
-    <row r="15" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="G14" s="39" t="s">
+        <v>167</v>
+      </c>
+      <c r="H14" s="39"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="8">
         <v>1896</v>
       </c>
@@ -18873,7 +19304,7 @@
         <v>0.76905150314611981</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <f>A16+1</f>
         <v>1897</v>
@@ -18904,7 +19335,7 @@
         <v>1.1447260834014719</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="8">
         <f t="shared" ref="A18:A36" si="3">A17+1</f>
         <v>1898</v>
@@ -18935,7 +19366,7 @@
         <v>3.4542314335060449E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -18966,7 +19397,7 @@
         <v>1.0711553175210407</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="8">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -18997,7 +19428,7 @@
         <v>2.3305537737866153</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -19028,7 +19459,7 @@
         <v>5.4061158328222199</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="8">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -19059,7 +19490,7 @@
         <v>7.1772055188530857</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="8">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -19090,7 +19521,7 @@
         <v>5.5701523909616393</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="8">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -19121,7 +19552,7 @@
         <v>7.0417936438833264</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="8">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -19152,7 +19583,7 @@
         <v>5.8077684314695697</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="8">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -19183,7 +19614,7 @@
         <v>5.8372604461200126</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -19214,7 +19645,7 @@
         <v>8.159514105330457</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="8">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -19245,7 +19676,7 @@
         <v>13.693419551160137</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="8">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -19276,7 +19707,7 @@
         <v>9.1432480191529386</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="8">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -19307,7 +19738,7 @@
         <v>11.441897961534032</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="8">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -19338,7 +19769,7 @@
         <v>13.023456612462224</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="8">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -19369,7 +19800,7 @@
         <v>13.15820198482195</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="8">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -19400,7 +19831,7 @@
         <v>9.6225471121240762</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="8">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -19431,7 +19862,7 @@
         <v>12.839879154078551</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="8">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -19462,7 +19893,7 @@
         <v>5.8097109177659272</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="8">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -19493,7 +19924,7 @@
         <v>5.6818181818181817</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>80</v>
       </c>
@@ -19540,14 +19971,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="13.578125" customWidth="1"/>
-    <col min="15" max="15" width="26.68359375" customWidth="1"/>
-    <col min="16" max="16" width="19.83984375" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="15" max="15" width="26.7109375" customWidth="1"/>
+    <col min="16" max="16" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
@@ -19588,11 +20019,11 @@
         <v>81</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="P1" s="10"/>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1896</v>
       </c>
@@ -19638,7 +20069,7 @@
       <c r="P2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1897</v>
       </c>
@@ -19684,7 +20115,7 @@
       <c r="P3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1898</v>
       </c>
@@ -19730,7 +20161,7 @@
       <c r="P4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1899</v>
       </c>
@@ -19776,7 +20207,7 @@
       <c r="P5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -19822,7 +20253,7 @@
       <c r="P6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>1901</v>
       </c>
@@ -19868,7 +20299,7 @@
       <c r="P7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>1902</v>
       </c>
@@ -19914,7 +20345,7 @@
       <c r="P8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>1903</v>
       </c>
@@ -19960,7 +20391,7 @@
       <c r="P9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>1904</v>
       </c>
@@ -20006,7 +20437,7 @@
       <c r="P10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>1905</v>
       </c>
@@ -20052,7 +20483,7 @@
       <c r="P11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>1906</v>
       </c>
@@ -20098,7 +20529,7 @@
       <c r="P12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>1907</v>
       </c>
@@ -20144,7 +20575,7 @@
       <c r="P13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>1908</v>
       </c>
@@ -20190,7 +20621,7 @@
       <c r="P14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>1909</v>
       </c>
@@ -20236,7 +20667,7 @@
       <c r="P15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>1910</v>
       </c>
@@ -20282,7 +20713,7 @@
       <c r="P16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>1911</v>
       </c>
@@ -20328,7 +20759,7 @@
       <c r="P17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>1912</v>
       </c>
@@ -20374,7 +20805,7 @@
       <c r="P18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>1913</v>
       </c>
@@ -20420,7 +20851,7 @@
       <c r="P19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>1914</v>
       </c>
@@ -20466,7 +20897,7 @@
       <c r="P20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>1915</v>
       </c>
@@ -20512,7 +20943,7 @@
       <c r="P21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>1916</v>
       </c>
@@ -20558,10 +20989,10 @@
       <c r="P22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="R24" s="4"/>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="F26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>

--- a/rtss-pre1917/src/main/resources/emigration-1896-1916.xlsx
+++ b/rtss-pre1917/src/main/resources/emigration-1896-1916.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\rtss-pre1917\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BBD8FF-01FB-46DE-BB25-1A7F529B5B9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C602E55B-2917-4449-97EA-BB83FBFBB367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1980" windowWidth="19785" windowHeight="18390" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{4A7477AA-BE08-4E7C-AEF1-FC3B0656E4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="note-1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="note-5" sheetId="7" r:id="rId5"/>
     <sheet name="data" sheetId="4" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -659,7 +664,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -815,14 +820,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,9 +847,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -882,7 +887,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -988,7 +993,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1130,7 +1135,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1139,24 +1144,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4E018E8-FFD2-476D-8A98-BDF34A70858D}">
   <dimension ref="A1:E97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.578125" customWidth="1"/>
+    <col min="3" max="3" width="20.83984375" customWidth="1"/>
+    <col min="4" max="4" width="24.578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="28.8">
       <c r="B5" s="2" t="s">
         <v>1</v>
       </c>
@@ -1168,7 +1173,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="B6" s="1">
         <v>1904</v>
       </c>
@@ -1179,7 +1184,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="B7" s="1">
         <v>1906</v>
       </c>
@@ -1190,7 +1195,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="B8" s="1">
         <v>1909</v>
       </c>
@@ -1201,7 +1206,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5">
       <c r="B9" s="1">
         <v>1910</v>
       </c>
@@ -1212,7 +1217,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5">
       <c r="B10" s="1">
         <v>1911</v>
       </c>
@@ -1223,7 +1228,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5">
       <c r="B11" s="1">
         <v>1912</v>
       </c>
@@ -1234,7 +1239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5">
       <c r="B12" s="1">
         <v>1913</v>
       </c>
@@ -1245,162 +1250,162 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2">
       <c r="B24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:2">
       <c r="B27" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2">
       <c r="B28" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:2">
       <c r="B30" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:2">
       <c r="B31" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:2">
       <c r="B32" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2">
       <c r="B34" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2">
       <c r="B35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2">
       <c r="B37" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2">
       <c r="B38" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2">
       <c r="B40" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2">
       <c r="B41" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2">
       <c r="B42" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2">
       <c r="A44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2">
       <c r="A45" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2">
       <c r="A46" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2">
       <c r="A48" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3">
       <c r="A51" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3">
       <c r="A53" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3">
       <c r="A55" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3">
       <c r="A56" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3">
       <c r="A57" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3">
       <c r="B59" s="1" t="s">
         <v>53</v>
       </c>
@@ -1408,7 +1413,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3">
       <c r="B60" s="1">
         <v>1896</v>
       </c>
@@ -1416,7 +1421,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3">
       <c r="B61" s="1">
         <f>B60+1</f>
         <v>1897</v>
@@ -1425,7 +1430,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3">
       <c r="B62" s="1">
         <f t="shared" ref="B62:B80" si="0">B61+1</f>
         <v>1898</v>
@@ -1434,7 +1439,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3">
       <c r="B63" s="1">
         <f t="shared" si="0"/>
         <v>1899</v>
@@ -1443,7 +1448,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3">
       <c r="B64" s="1">
         <f t="shared" si="0"/>
         <v>1900</v>
@@ -1452,7 +1457,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:3">
       <c r="B65" s="1">
         <f t="shared" si="0"/>
         <v>1901</v>
@@ -1461,7 +1466,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:3">
       <c r="B66" s="1">
         <f t="shared" si="0"/>
         <v>1902</v>
@@ -1470,7 +1475,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:3">
       <c r="B67" s="1">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -1479,7 +1484,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:3">
       <c r="B68" s="1">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -1488,7 +1493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:3">
       <c r="B69" s="1">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -1497,7 +1502,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:3">
       <c r="B70" s="1">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -1506,7 +1511,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:3">
       <c r="B71" s="1">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -1515,7 +1520,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:3">
       <c r="B72" s="1">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -1524,7 +1529,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:3">
       <c r="B73" s="1">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -1533,7 +1538,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:3">
       <c r="B74" s="1">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -1542,7 +1547,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:3">
       <c r="B75" s="1">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -1551,7 +1556,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:3">
       <c r="B76" s="1">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -1560,7 +1565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:3">
       <c r="B77" s="1">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -1569,7 +1574,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:3">
       <c r="B78" s="1">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -1578,7 +1583,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:3">
       <c r="B79" s="1">
         <f t="shared" si="0"/>
         <v>1915</v>
@@ -1587,7 +1592,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:3">
       <c r="B80" s="1">
         <f t="shared" si="0"/>
         <v>1916</v>
@@ -1596,7 +1601,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3">
       <c r="B81" s="1">
         <v>1917</v>
       </c>
@@ -1604,22 +1609,22 @@
         <v>63</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3">
       <c r="A83" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3">
       <c r="A84" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3">
       <c r="A86" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3">
       <c r="B88" s="1">
         <v>1908</v>
       </c>
@@ -1627,7 +1632,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3">
       <c r="B89" s="1">
         <f t="shared" ref="B89:B96" si="1">B88+1</f>
         <v>1909</v>
@@ -1636,7 +1641,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3">
       <c r="B90" s="1">
         <f t="shared" si="1"/>
         <v>1910</v>
@@ -1645,7 +1650,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3">
       <c r="B91" s="1">
         <f t="shared" si="1"/>
         <v>1911</v>
@@ -1654,7 +1659,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3">
       <c r="B92" s="1">
         <f t="shared" si="1"/>
         <v>1912</v>
@@ -1663,7 +1668,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3">
       <c r="B93" s="1">
         <f t="shared" si="1"/>
         <v>1913</v>
@@ -1672,7 +1677,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3">
       <c r="B94" s="1">
         <f t="shared" si="1"/>
         <v>1914</v>
@@ -1681,7 +1686,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3">
       <c r="B95" s="1">
         <f t="shared" si="1"/>
         <v>1915</v>
@@ -1690,7 +1695,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3">
       <c r="B96" s="1">
         <f t="shared" si="1"/>
         <v>1916</v>
@@ -1699,7 +1704,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3">
       <c r="B97" s="1">
         <v>1917</v>
       </c>
@@ -1715,14 +1720,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7496F63D-12C4-4F78-B39E-C61E39C373AD}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="4" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" customWidth="1"/>
+    <col min="4" max="4" width="10.41796875" customWidth="1"/>
+    <col min="5" max="5" width="12.41796875" customWidth="1"/>
+    <col min="6" max="6" width="27.15625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="43.2">
       <c r="A1" s="7" t="s">
         <v>19</v>
       </c>
@@ -1763,7 +1768,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20">
       <c r="A2" s="1">
         <v>1896</v>
       </c>
@@ -1806,7 +1811,7 @@
         <v>52136</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20">
       <c r="A3" s="1">
         <f>A2+1</f>
         <v>1897</v>
@@ -1848,7 +1853,7 @@
         <v>29981</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20">
       <c r="A4" s="1">
         <f t="shared" ref="A4:A22" si="3">A3+1</f>
         <v>1898</v>
@@ -1890,7 +1895,7 @@
         <v>34554</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20">
       <c r="A5" s="1">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -1914,7 +1919,7 @@
         <v>57773.68421052632</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20">
       <c r="A6" s="1">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -1938,7 +1943,7 @@
         <v>82289.473684210534</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20">
       <c r="A7" s="1">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -1962,7 +1967,7 @@
         <v>79218.947368421053</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20">
       <c r="A8" s="1">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -1986,7 +1991,7 @@
         <v>98398.947368421053</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20">
       <c r="A9" s="1">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -2010,7 +2015,7 @@
         <v>123398.94736842105</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20">
       <c r="A10" s="1">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -2034,7 +2039,7 @@
         <v>142088.42105263157</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20">
       <c r="A11" s="1">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -2058,7 +2063,7 @@
         <v>176721.05263157896</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20">
       <c r="A12" s="1">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -2082,7 +2087,7 @@
         <v>212135.78947368421</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20">
       <c r="A13" s="1">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -2106,7 +2111,7 @@
         <v>256929.47368421053</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20">
       <c r="A14" s="1">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -2130,7 +2135,7 @@
         <v>157857.89473684211</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20">
       <c r="A15" s="1">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -2154,7 +2159,7 @@
         <v>114497.89473684211</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20">
       <c r="A16" s="1">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -2178,7 +2183,7 @@
         <v>180058.94736842107</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" s="1">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -2202,7 +2207,7 @@
         <v>156781.05263157896</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" s="1">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -2226,7 +2231,7 @@
         <v>163951.57894736843</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" s="1">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -2250,7 +2255,7 @@
         <v>292930.5263157895</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" s="1">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -2274,7 +2279,7 @@
         <v>255636.84210526317</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" s="1">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -2298,7 +2303,7 @@
         <v>23910.526315789473</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" s="1">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -2322,7 +2327,7 @@
         <v>2308.4210526315792</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>49</v>
       </c>
@@ -2347,7 +2352,7 @@
         <v>2687088.4210526319</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
     </row>
@@ -2359,58 +2364,58 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54424CF4-C226-4A4F-8C1B-D8A2CB8D4757}">
   <dimension ref="A1:AI310"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" customWidth="1"/>
-    <col min="10" max="10" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.578125" customWidth="1"/>
+    <col min="2" max="2" width="7.26171875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.15625" customWidth="1"/>
+    <col min="4" max="4" width="7.578125" customWidth="1"/>
+    <col min="5" max="5" width="5.68359375" customWidth="1"/>
+    <col min="6" max="6" width="9.578125" customWidth="1"/>
+    <col min="7" max="7" width="8.15625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.68359375" customWidth="1"/>
+    <col min="9" max="9" width="7.578125" customWidth="1"/>
+    <col min="10" max="10" width="7.15625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.15625" customWidth="1"/>
+    <col min="13" max="13" width="6.83984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.41796875" customWidth="1"/>
+    <col min="17" max="17" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.83984375" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:35">
       <c r="A1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35">
       <c r="A3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35">
       <c r="A5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35">
       <c r="A6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35">
       <c r="A7" t="s">
         <v>83</v>
       </c>
@@ -2418,7 +2423,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35">
       <c r="P9" s="14" t="s">
         <v>71</v>
       </c>
@@ -2451,7 +2456,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35">
       <c r="A10" s="10" t="s">
         <v>84</v>
       </c>
@@ -2534,7 +2539,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35">
       <c r="A11" s="1">
         <v>1896</v>
       </c>
@@ -2588,7 +2593,7 @@
       </c>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35">
       <c r="A12" s="1">
         <f>A11+1</f>
         <v>1897</v>
@@ -2643,7 +2648,7 @@
       </c>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35">
       <c r="A13" s="1">
         <f t="shared" ref="A13:A31" si="2">A12+1</f>
         <v>1898</v>
@@ -2698,7 +2703,7 @@
       </c>
       <c r="P13" s="4"/>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35">
       <c r="A14" s="1">
         <f t="shared" si="2"/>
         <v>1899</v>
@@ -2796,7 +2801,7 @@
         <v>4.3528753924899997</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35">
       <c r="A15" s="1">
         <f t="shared" si="2"/>
         <v>1900</v>
@@ -2894,7 +2899,7 @@
         <v>5.6415392085457636</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35">
       <c r="A16" s="1">
         <f t="shared" si="2"/>
         <v>1901</v>
@@ -2992,7 +2997,7 @@
         <v>2.5448767286540708</v>
       </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35">
       <c r="A17" s="1">
         <f t="shared" si="2"/>
         <v>1902</v>
@@ -3090,7 +3095,7 @@
         <v>3.0960917891717461</v>
       </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35">
       <c r="A18" s="1">
         <f t="shared" si="2"/>
         <v>1903</v>
@@ -3188,7 +3193,7 @@
         <v>1.9799110237312059</v>
       </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35">
       <c r="A19" s="1">
         <f t="shared" si="2"/>
         <v>1904</v>
@@ -3286,7 +3291,7 @@
         <v>1.427190352127677</v>
       </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35">
       <c r="A20" s="1">
         <f t="shared" si="2"/>
         <v>1905</v>
@@ -3384,7 +3389,7 @@
         <v>1.1078286558345642</v>
       </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35">
       <c r="A21" s="1">
         <f t="shared" si="2"/>
         <v>1906</v>
@@ -3482,7 +3487,7 @@
         <v>1.61159938769543</v>
       </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35">
       <c r="A22" s="1">
         <f t="shared" si="2"/>
         <v>1907</v>
@@ -3580,7 +3585,7 @@
         <v>2.650444548432382</v>
       </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35">
       <c r="A23" s="1">
         <f t="shared" si="2"/>
         <v>1908</v>
@@ -3678,7 +3683,7 @@
         <v>1.6072463326115465</v>
       </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35">
       <c r="A24" s="1">
         <f t="shared" si="2"/>
         <v>1909</v>
@@ -3776,7 +3781,7 @@
         <v>1.6887644302205966</v>
       </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35">
       <c r="A25" s="1">
         <f t="shared" si="2"/>
         <v>1910</v>
@@ -3874,7 +3879,7 @@
         <v>2.6865499548398257</v>
       </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>1911</v>
@@ -3972,7 +3977,7 @@
         <v>1.5918358446542664</v>
       </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>1912</v>
@@ -4070,7 +4075,7 @@
         <v>1.3100851238884845</v>
       </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>1913</v>
@@ -4168,7 +4173,7 @@
         <v>2.3027080052662829</v>
       </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>1914</v>
@@ -4266,7 +4271,7 @@
         <v>2.0608548525781489</v>
       </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>1915</v>
@@ -4364,7 +4369,7 @@
         <v>0.49870172690928577</v>
       </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>1916</v>
@@ -4462,7 +4467,7 @@
         <v>1.3926559566033798</v>
       </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35">
       <c r="A32" s="1">
         <v>1917</v>
       </c>
@@ -4559,7 +4564,7 @@
         <v>5.8184812868690303E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35">
       <c r="P33" s="17">
         <f>SUM(P14:P31)-P32</f>
         <v>0</v>
@@ -4602,7 +4607,7 @@
       </c>
       <c r="AI33" s="4"/>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35">
       <c r="A34" t="s">
         <v>85</v>
       </c>
@@ -4655,7 +4660,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4708,12 +4713,12 @@
         <v>0.1375376540970189</v>
       </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35">
       <c r="A40" s="10" t="s">
         <v>87</v>
       </c>
@@ -4757,7 +4762,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35">
       <c r="A41" s="1">
         <v>1896</v>
       </c>
@@ -4814,7 +4819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35">
       <c r="A42" s="1">
         <f>A41+1</f>
         <v>1897</v>
@@ -4872,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35">
       <c r="A43" s="1">
         <f t="shared" ref="A43:A60" si="17">A42+1</f>
         <v>1898</v>
@@ -4930,7 +4935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35">
       <c r="A44" s="1">
         <f t="shared" si="17"/>
         <v>1899</v>
@@ -4988,7 +4993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35">
       <c r="A45" s="1">
         <f t="shared" si="17"/>
         <v>1900</v>
@@ -5046,7 +5051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35">
       <c r="A46" s="1">
         <f t="shared" si="17"/>
         <v>1901</v>
@@ -5104,7 +5109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35">
       <c r="A47" s="1">
         <f t="shared" si="17"/>
         <v>1902</v>
@@ -5162,7 +5167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35">
       <c r="A48" s="1">
         <f t="shared" si="17"/>
         <v>1903</v>
@@ -5220,7 +5225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="A49" s="1">
         <f t="shared" si="17"/>
         <v>1904</v>
@@ -5278,7 +5283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15">
       <c r="A50" s="1">
         <f t="shared" si="17"/>
         <v>1905</v>
@@ -5336,7 +5341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="A51" s="1">
         <f t="shared" si="17"/>
         <v>1906</v>
@@ -5394,7 +5399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15">
       <c r="A52" s="1">
         <f t="shared" si="17"/>
         <v>1907</v>
@@ -5452,7 +5457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53" s="1">
         <f t="shared" si="17"/>
         <v>1908</v>
@@ -5510,7 +5515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15">
       <c r="A54" s="1">
         <f t="shared" si="17"/>
         <v>1909</v>
@@ -5568,7 +5573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15">
       <c r="A55" s="1">
         <f t="shared" si="17"/>
         <v>1910</v>
@@ -5626,7 +5631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15">
       <c r="A56" s="1">
         <f t="shared" si="17"/>
         <v>1911</v>
@@ -5684,7 +5689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15">
       <c r="A57" s="1">
         <f t="shared" si="17"/>
         <v>1912</v>
@@ -5742,7 +5747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15">
       <c r="A58" s="1">
         <f t="shared" si="17"/>
         <v>1913</v>
@@ -5800,7 +5805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15">
       <c r="A59" s="1">
         <f t="shared" si="17"/>
         <v>1914</v>
@@ -5858,7 +5863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15">
       <c r="A60" s="1">
         <f t="shared" si="17"/>
         <v>1915</v>
@@ -5916,7 +5921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15">
       <c r="A61" s="1">
         <v>1916</v>
       </c>
@@ -5973,7 +5978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15">
       <c r="A62" s="11" t="s">
         <v>49</v>
       </c>
@@ -6030,7 +6035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15">
       <c r="A63" s="11" t="s">
         <v>88</v>
       </c>
@@ -6083,12 +6088,12 @@
         <v>0.12899442300236147</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19">
       <c r="A66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19">
       <c r="A68" s="10" t="s">
         <v>84</v>
       </c>
@@ -6129,7 +6134,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19">
       <c r="A69" s="1">
         <v>1908</v>
       </c>
@@ -6171,7 +6176,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19">
       <c r="A70" s="1">
         <f t="shared" ref="A70:A76" si="39">A69+1</f>
         <v>1909</v>
@@ -6214,7 +6219,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19">
       <c r="A71" s="1">
         <f t="shared" si="39"/>
         <v>1910</v>
@@ -6257,7 +6262,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:19">
       <c r="A72" s="1">
         <f t="shared" si="39"/>
         <v>1911</v>
@@ -6283,7 +6288,7 @@
       </c>
       <c r="M72" s="4"/>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19">
       <c r="A73" s="1">
         <f t="shared" si="39"/>
         <v>1912</v>
@@ -6326,7 +6331,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19">
       <c r="A74" s="1">
         <f t="shared" si="39"/>
         <v>1913</v>
@@ -6352,7 +6357,7 @@
       </c>
       <c r="M74" s="4"/>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19">
       <c r="A75" s="1">
         <f t="shared" si="39"/>
         <v>1914</v>
@@ -6395,7 +6400,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19">
       <c r="A76" s="1">
         <f t="shared" si="39"/>
         <v>1915</v>
@@ -6447,7 +6452,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19">
       <c r="A77" s="1">
         <v>1916</v>
       </c>
@@ -6497,7 +6502,7 @@
         <v>1.1658168920416758</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19">
       <c r="A78" s="1">
         <v>1917</v>
       </c>
@@ -6527,12 +6532,12 @@
         <v>178</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19">
       <c r="A80" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13">
       <c r="A82" s="10" t="s">
         <v>84</v>
       </c>
@@ -6573,7 +6578,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13">
       <c r="A83" s="1">
         <v>1908</v>
       </c>
@@ -6615,7 +6620,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13">
       <c r="A84" s="1">
         <f t="shared" ref="A84:A90" si="41">A83+1</f>
         <v>1909</v>
@@ -6658,7 +6663,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13">
       <c r="A85" s="1">
         <f t="shared" si="41"/>
         <v>1910</v>
@@ -6701,7 +6706,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13">
       <c r="A86" s="1">
         <f t="shared" si="41"/>
         <v>1911</v>
@@ -6727,7 +6732,7 @@
       </c>
       <c r="M86" s="4"/>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13">
       <c r="A87" s="1">
         <f t="shared" si="41"/>
         <v>1912</v>
@@ -6770,7 +6775,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13">
       <c r="A88" s="1">
         <f t="shared" si="41"/>
         <v>1913</v>
@@ -6796,7 +6801,7 @@
       </c>
       <c r="M88" s="4"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13">
       <c r="A89" s="1">
         <f t="shared" si="41"/>
         <v>1914</v>
@@ -6839,7 +6844,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13">
       <c r="A90" s="1">
         <f t="shared" si="41"/>
         <v>1915</v>
@@ -6882,7 +6887,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13">
       <c r="A91" s="1">
         <v>1916</v>
       </c>
@@ -6924,7 +6929,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13">
       <c r="A92" s="1">
         <v>1917</v>
       </c>
@@ -6949,12 +6954,12 @@
       </c>
       <c r="M92" s="4"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13">
       <c r="A94" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13">
       <c r="B96" s="10" t="s">
         <v>70</v>
       </c>
@@ -6992,7 +6997,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13">
       <c r="A97" t="s">
         <v>143</v>
       </c>
@@ -7045,7 +7050,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13">
       <c r="A98" t="s">
         <v>144</v>
       </c>
@@ -7098,7 +7103,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13">
       <c r="A99" t="s">
         <v>145</v>
       </c>
@@ -7151,7 +7156,7 @@
         <v>54.280155642023345</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13">
       <c r="B100" s="26"/>
       <c r="C100" s="26"/>
       <c r="D100" s="26"/>
@@ -7165,7 +7170,7 @@
       <c r="L100" s="26"/>
       <c r="M100" s="26"/>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13">
       <c r="A101" t="s">
         <v>152</v>
       </c>
@@ -7182,7 +7187,7 @@
       <c r="L101" s="26"/>
       <c r="M101" s="26"/>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13">
       <c r="B102" s="26"/>
       <c r="C102" s="26"/>
       <c r="D102" s="26"/>
@@ -7196,7 +7201,7 @@
       <c r="L102" s="26"/>
       <c r="M102" s="26"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13">
       <c r="B103" s="10" t="s">
         <v>70</v>
       </c>
@@ -7234,7 +7239,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13">
       <c r="A104" t="s">
         <v>143</v>
       </c>
@@ -7287,7 +7292,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13">
       <c r="A105" t="s">
         <v>144</v>
       </c>
@@ -7340,7 +7345,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13">
       <c r="A106" t="s">
         <v>145</v>
       </c>
@@ -7393,7 +7398,7 @@
         <v>47.149894440534837</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13">
       <c r="B107" s="26"/>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
@@ -7407,7 +7412,7 @@
       <c r="L107" s="26"/>
       <c r="M107" s="26"/>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13">
       <c r="A108" t="s">
         <v>153</v>
       </c>
@@ -7424,7 +7429,7 @@
       <c r="L108" s="26"/>
       <c r="M108" s="26"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13">
       <c r="A109" t="s">
         <v>154</v>
       </c>
@@ -7441,7 +7446,7 @@
       <c r="L109" s="26"/>
       <c r="M109" s="26"/>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13">
       <c r="B110" s="26"/>
       <c r="C110" s="26"/>
       <c r="D110" s="26"/>
@@ -7455,7 +7460,7 @@
       <c r="L110" s="26"/>
       <c r="M110" s="26"/>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13">
       <c r="B111" s="10" t="s">
         <v>70</v>
       </c>
@@ -7493,7 +7498,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13">
       <c r="B112" s="26">
         <f>B106</f>
         <v>6.9984447900466566</v>
@@ -7543,12 +7548,12 @@
         <v>50.715025041279091</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:16">
       <c r="A114" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:16">
       <c r="A116" s="10" t="s">
         <v>84</v>
       </c>
@@ -7595,7 +7600,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:16">
       <c r="A117" s="1">
         <v>1896</v>
       </c>
@@ -7652,7 +7657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:16">
       <c r="A118" s="1">
         <f>A117+1</f>
         <v>1897</v>
@@ -7710,7 +7715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:16">
       <c r="A119" s="1">
         <f t="shared" ref="A119:A137" si="54">A118+1</f>
         <v>1898</v>
@@ -7768,7 +7773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:16">
       <c r="A120" s="1">
         <f t="shared" si="54"/>
         <v>1899</v>
@@ -7826,7 +7831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:16">
       <c r="A121" s="1">
         <f t="shared" si="54"/>
         <v>1900</v>
@@ -7884,7 +7889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:16">
       <c r="A122" s="1">
         <f t="shared" si="54"/>
         <v>1901</v>
@@ -7942,7 +7947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:16">
       <c r="A123" s="1">
         <f t="shared" si="54"/>
         <v>1902</v>
@@ -8000,7 +8005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:16">
       <c r="A124" s="1">
         <f t="shared" si="54"/>
         <v>1903</v>
@@ -8058,7 +8063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:16">
       <c r="A125" s="1">
         <f t="shared" si="54"/>
         <v>1904</v>
@@ -8116,7 +8121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:16">
       <c r="A126" s="1">
         <f t="shared" si="54"/>
         <v>1905</v>
@@ -8174,7 +8179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:16">
       <c r="A127" s="1">
         <f t="shared" si="54"/>
         <v>1906</v>
@@ -8232,7 +8237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:16">
       <c r="A128" s="1">
         <f t="shared" si="54"/>
         <v>1907</v>
@@ -8290,7 +8295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16">
       <c r="A129" s="1">
         <f t="shared" si="54"/>
         <v>1908</v>
@@ -8337,7 +8342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16">
       <c r="A130" s="1">
         <f t="shared" si="54"/>
         <v>1909</v>
@@ -8384,7 +8389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16">
       <c r="A131" s="1">
         <f t="shared" si="54"/>
         <v>1910</v>
@@ -8431,7 +8436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16">
       <c r="A132" s="1">
         <f t="shared" si="54"/>
         <v>1911</v>
@@ -8489,7 +8494,7 @@
         <v>15723.438359773389</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16">
       <c r="A133" s="1">
         <f t="shared" si="54"/>
         <v>1912</v>
@@ -8536,7 +8541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16">
       <c r="A134" s="1">
         <f t="shared" si="54"/>
         <v>1913</v>
@@ -8594,7 +8599,7 @@
         <v>36173.276557684701</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16">
       <c r="A135" s="1">
         <f t="shared" si="54"/>
         <v>1914</v>
@@ -8641,7 +8646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16">
       <c r="A136" s="1">
         <f t="shared" si="54"/>
         <v>1915</v>
@@ -8688,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16">
       <c r="A137" s="1">
         <f t="shared" si="54"/>
         <v>1916</v>
@@ -8735,7 +8740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16">
       <c r="A138" s="1">
         <v>1917</v>
       </c>
@@ -8792,7 +8797,7 @@
         <v>639.69124188047317</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16">
       <c r="A139" s="1"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -8807,7 +8812,7 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16">
       <c r="A140" s="30" t="s">
         <v>174</v>
       </c>
@@ -8824,7 +8829,7 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16">
       <c r="A141" s="1"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -8839,7 +8844,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16">
       <c r="A142" s="1">
         <v>1911</v>
       </c>
@@ -8880,7 +8885,7 @@
         <v>-11.876056132993654</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16">
       <c r="A143" s="1">
         <f>A142+1</f>
         <v>1912</v>
@@ -8898,7 +8903,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16">
       <c r="A144" s="1">
         <f t="shared" ref="A144:A148" si="74">A143+1</f>
         <v>1913</v>
@@ -8940,7 +8945,7 @@
         <v>116.94950349421394</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15">
       <c r="A145" s="1">
         <f t="shared" si="74"/>
         <v>1914</v>
@@ -8958,7 +8963,7 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15">
       <c r="A146" s="1">
         <f t="shared" si="74"/>
         <v>1915</v>
@@ -8976,7 +8981,7 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15">
       <c r="A147" s="1">
         <f t="shared" si="74"/>
         <v>1916</v>
@@ -8994,7 +8999,7 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15">
       <c r="A148" s="1">
         <f t="shared" si="74"/>
         <v>1917</v>
@@ -9036,7 +9041,7 @@
         <v>218.84913831012869</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15">
       <c r="A149" s="1"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -9051,7 +9056,7 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15">
       <c r="A150" s="30" t="s">
         <v>172</v>
       </c>
@@ -9068,7 +9073,7 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15">
       <c r="A151" s="1"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -9083,7 +9088,7 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15">
       <c r="A152" s="10" t="str">
         <f t="shared" ref="A152:M152" si="76">A116</f>
         <v>фин. год</v>
@@ -9142,7 +9147,7 @@
         <v>разница</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15">
       <c r="A153" s="1">
         <f t="shared" ref="A153:M153" si="77">A117</f>
         <v>1896</v>
@@ -9201,7 +9206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15">
       <c r="A154" s="1">
         <f t="shared" ref="A154:M154" si="79">A118</f>
         <v>1897</v>
@@ -9260,7 +9265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15">
       <c r="A155" s="1">
         <f t="shared" ref="A155:M155" si="80">A119</f>
         <v>1898</v>
@@ -9319,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15">
       <c r="A156" s="1">
         <f t="shared" ref="A156:M156" si="81">A120</f>
         <v>1899</v>
@@ -9378,7 +9383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15">
       <c r="A157" s="1">
         <f t="shared" ref="A157:M157" si="82">A121</f>
         <v>1900</v>
@@ -9437,7 +9442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15">
       <c r="A158" s="1">
         <f t="shared" ref="A158:M158" si="83">A122</f>
         <v>1901</v>
@@ -9496,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15">
       <c r="A159" s="1">
         <f t="shared" ref="A159:M159" si="84">A123</f>
         <v>1902</v>
@@ -9555,7 +9560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15">
       <c r="A160" s="1">
         <f t="shared" ref="A160:M160" si="85">A124</f>
         <v>1903</v>
@@ -9614,7 +9619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15">
       <c r="A161" s="1">
         <f t="shared" ref="A161:M161" si="86">A125</f>
         <v>1904</v>
@@ -9673,7 +9678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15">
       <c r="A162" s="1">
         <f t="shared" ref="A162:M162" si="87">A126</f>
         <v>1905</v>
@@ -9732,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15">
       <c r="A163" s="1">
         <f t="shared" ref="A163:M163" si="88">A127</f>
         <v>1906</v>
@@ -9791,7 +9796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15">
       <c r="A164" s="1">
         <f t="shared" ref="A164:M164" si="89">A128</f>
         <v>1907</v>
@@ -9850,7 +9855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15">
       <c r="A165" s="1">
         <f t="shared" ref="A165:M165" si="90">A129</f>
         <v>1908</v>
@@ -9909,7 +9914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15">
       <c r="A166" s="1">
         <f t="shared" ref="A166:M166" si="91">A130</f>
         <v>1909</v>
@@ -9968,7 +9973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15">
       <c r="A167" s="1">
         <f t="shared" ref="A167:M167" si="92">A131</f>
         <v>1910</v>
@@ -10027,7 +10032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15">
       <c r="A168" s="1">
         <f t="shared" ref="A168:A174" si="93">A132</f>
         <v>1911</v>
@@ -10086,7 +10091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15">
       <c r="A169" s="1">
         <f t="shared" si="93"/>
         <v>1912</v>
@@ -10145,7 +10150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15">
       <c r="A170" s="1">
         <f t="shared" si="93"/>
         <v>1913</v>
@@ -10204,7 +10209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15">
       <c r="A171" s="1">
         <f t="shared" si="93"/>
         <v>1914</v>
@@ -10263,7 +10268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15">
       <c r="A172" s="1">
         <f t="shared" si="93"/>
         <v>1915</v>
@@ -10322,7 +10327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15">
       <c r="A173" s="1">
         <f t="shared" si="93"/>
         <v>1916</v>
@@ -10381,7 +10386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15">
       <c r="A174" s="1">
         <f t="shared" si="93"/>
         <v>1917</v>
@@ -10440,12 +10445,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15">
       <c r="A176" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16">
       <c r="A178" s="10" t="s">
         <v>84</v>
       </c>
@@ -10489,7 +10494,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16">
       <c r="A179" s="1">
         <v>1896</v>
       </c>
@@ -10547,7 +10552,7 @@
       </c>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16">
       <c r="A180" s="1">
         <f>A179+1</f>
         <v>1897</v>
@@ -10606,7 +10611,7 @@
       </c>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16">
       <c r="A181" s="1">
         <f t="shared" ref="A181:A199" si="104">A180+1</f>
         <v>1898</v>
@@ -10665,7 +10670,7 @@
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16">
       <c r="A182" s="1">
         <f t="shared" si="104"/>
         <v>1899</v>
@@ -10724,7 +10729,7 @@
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16">
       <c r="A183" s="1">
         <f t="shared" si="104"/>
         <v>1900</v>
@@ -10783,7 +10788,7 @@
       </c>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16">
       <c r="A184" s="1">
         <f t="shared" si="104"/>
         <v>1901</v>
@@ -10842,7 +10847,7 @@
       </c>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16">
       <c r="A185" s="1">
         <f t="shared" si="104"/>
         <v>1902</v>
@@ -10901,7 +10906,7 @@
       </c>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16">
       <c r="A186" s="1">
         <f t="shared" si="104"/>
         <v>1903</v>
@@ -10960,7 +10965,7 @@
       </c>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16">
       <c r="A187" s="1">
         <f t="shared" si="104"/>
         <v>1904</v>
@@ -11019,7 +11024,7 @@
       </c>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16">
       <c r="A188" s="1">
         <f t="shared" si="104"/>
         <v>1905</v>
@@ -11078,7 +11083,7 @@
       </c>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16">
       <c r="A189" s="1">
         <f t="shared" si="104"/>
         <v>1906</v>
@@ -11137,7 +11142,7 @@
       </c>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16">
       <c r="A190" s="1">
         <f t="shared" si="104"/>
         <v>1907</v>
@@ -11196,7 +11201,7 @@
       </c>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16">
       <c r="A191" s="1">
         <f t="shared" si="104"/>
         <v>1908</v>
@@ -11254,7 +11259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16">
       <c r="A192" s="1">
         <f t="shared" si="104"/>
         <v>1909</v>
@@ -11312,7 +11317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15">
       <c r="A193" s="1">
         <f t="shared" si="104"/>
         <v>1910</v>
@@ -11370,7 +11375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15">
       <c r="A194" s="1">
         <f t="shared" si="104"/>
         <v>1911</v>
@@ -11428,7 +11433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15">
       <c r="A195" s="1">
         <f t="shared" si="104"/>
         <v>1912</v>
@@ -11486,7 +11491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15">
       <c r="A196" s="1">
         <f t="shared" si="104"/>
         <v>1913</v>
@@ -11544,7 +11549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15">
       <c r="A197" s="1">
         <f t="shared" si="104"/>
         <v>1914</v>
@@ -11602,7 +11607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15">
       <c r="A198" s="1">
         <f t="shared" si="104"/>
         <v>1915</v>
@@ -11660,7 +11665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15">
       <c r="A199" s="1">
         <f t="shared" si="104"/>
         <v>1916</v>
@@ -11718,7 +11723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15">
       <c r="A200" s="1">
         <v>1917</v>
       </c>
@@ -11775,12 +11780,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15">
       <c r="A202" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15">
       <c r="A204" s="10" t="s">
         <v>87</v>
       </c>
@@ -11824,7 +11829,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15">
       <c r="A205" s="1">
         <v>1896</v>
       </c>
@@ -11881,7 +11886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15">
       <c r="A206" s="1">
         <f>A205+1</f>
         <v>1897</v>
@@ -11939,7 +11944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15">
       <c r="A207" s="1">
         <f t="shared" ref="A207:A224" si="128">A206+1</f>
         <v>1898</v>
@@ -11997,7 +12002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15">
       <c r="A208" s="1">
         <f t="shared" si="128"/>
         <v>1899</v>
@@ -12055,7 +12060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15">
       <c r="A209" s="1">
         <f t="shared" si="128"/>
         <v>1900</v>
@@ -12113,7 +12118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15">
       <c r="A210" s="1">
         <f t="shared" si="128"/>
         <v>1901</v>
@@ -12171,7 +12176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15">
       <c r="A211" s="1">
         <f t="shared" si="128"/>
         <v>1902</v>
@@ -12229,7 +12234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15">
       <c r="A212" s="1">
         <f t="shared" si="128"/>
         <v>1903</v>
@@ -12287,7 +12292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15">
       <c r="A213" s="1">
         <f t="shared" si="128"/>
         <v>1904</v>
@@ -12345,7 +12350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15">
       <c r="A214" s="1">
         <f t="shared" si="128"/>
         <v>1905</v>
@@ -12403,7 +12408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15">
       <c r="A215" s="1">
         <f t="shared" si="128"/>
         <v>1906</v>
@@ -12461,7 +12466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15">
       <c r="A216" s="1">
         <f t="shared" si="128"/>
         <v>1907</v>
@@ -12519,7 +12524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15">
       <c r="A217" s="1">
         <f t="shared" si="128"/>
         <v>1908</v>
@@ -12577,7 +12582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15">
       <c r="A218" s="1">
         <f t="shared" si="128"/>
         <v>1909</v>
@@ -12635,7 +12640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15">
       <c r="A219" s="1">
         <f t="shared" si="128"/>
         <v>1910</v>
@@ -12693,7 +12698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15">
       <c r="A220" s="1">
         <f t="shared" si="128"/>
         <v>1911</v>
@@ -12751,7 +12756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15">
       <c r="A221" s="1">
         <f t="shared" si="128"/>
         <v>1912</v>
@@ -12809,7 +12814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15">
       <c r="A222" s="1">
         <f t="shared" si="128"/>
         <v>1913</v>
@@ -12867,7 +12872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15">
       <c r="A223" s="1">
         <f t="shared" si="128"/>
         <v>1914</v>
@@ -12925,7 +12930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15">
       <c r="A224" s="1">
         <f t="shared" si="128"/>
         <v>1915</v>
@@ -12983,7 +12988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15">
       <c r="A225" s="1">
         <v>1916</v>
       </c>
@@ -13040,7 +13045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15">
       <c r="A226" s="11" t="s">
         <v>49</v>
       </c>
@@ -13097,7 +13102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15">
       <c r="A227" s="11" t="s">
         <v>88</v>
       </c>
@@ -13150,15 +13155,15 @@
         <v>8.2845503895924058E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15">
       <c r="A229" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15">
       <c r="L230" s="4"/>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15">
       <c r="A231" t="s">
         <v>181</v>
       </c>
@@ -13167,10 +13172,10 @@
       </c>
       <c r="L231" s="4"/>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15">
       <c r="L232" s="4"/>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15">
       <c r="A233" s="10" t="s">
         <v>87</v>
       </c>
@@ -13214,7 +13219,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15">
       <c r="A234" s="1">
         <v>1896</v>
       </c>
@@ -13271,7 +13276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15">
       <c r="A235" s="1">
         <f>A234+1</f>
         <v>1897</v>
@@ -13329,7 +13334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15">
       <c r="A236" s="1">
         <f t="shared" ref="A236:A253" si="153">A235+1</f>
         <v>1898</v>
@@ -13387,7 +13392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15">
       <c r="A237" s="1">
         <f t="shared" si="153"/>
         <v>1899</v>
@@ -13445,7 +13450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15">
       <c r="A238" s="1">
         <f t="shared" si="153"/>
         <v>1900</v>
@@ -13503,7 +13508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15">
       <c r="A239" s="1">
         <f t="shared" si="153"/>
         <v>1901</v>
@@ -13561,7 +13566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15">
       <c r="A240" s="1">
         <f t="shared" si="153"/>
         <v>1902</v>
@@ -13619,7 +13624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15">
       <c r="A241" s="1">
         <f t="shared" si="153"/>
         <v>1903</v>
@@ -13677,7 +13682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15">
       <c r="A242" s="1">
         <f t="shared" si="153"/>
         <v>1904</v>
@@ -13735,7 +13740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15">
       <c r="A243" s="1">
         <f t="shared" si="153"/>
         <v>1905</v>
@@ -13793,7 +13798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15">
       <c r="A244" s="1">
         <f t="shared" si="153"/>
         <v>1906</v>
@@ -13851,7 +13856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15">
       <c r="A245" s="1">
         <f t="shared" si="153"/>
         <v>1907</v>
@@ -13909,7 +13914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15">
       <c r="A246" s="1">
         <f t="shared" si="153"/>
         <v>1908</v>
@@ -13967,7 +13972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15">
       <c r="A247" s="1">
         <f t="shared" si="153"/>
         <v>1909</v>
@@ -14025,7 +14030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15">
       <c r="A248" s="1">
         <f t="shared" si="153"/>
         <v>1910</v>
@@ -14083,7 +14088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15">
       <c r="A249" s="1">
         <f t="shared" si="153"/>
         <v>1911</v>
@@ -14141,7 +14146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15">
       <c r="A250" s="1">
         <f t="shared" si="153"/>
         <v>1912</v>
@@ -14199,7 +14204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15">
       <c r="A251" s="1">
         <f t="shared" si="153"/>
         <v>1913</v>
@@ -14257,7 +14262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15">
       <c r="A252" s="1">
         <f t="shared" si="153"/>
         <v>1914</v>
@@ -14315,7 +14320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15">
       <c r="A253" s="1">
         <f t="shared" si="153"/>
         <v>1915</v>
@@ -14373,7 +14378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15">
       <c r="A254" s="1">
         <v>1916</v>
       </c>
@@ -14430,7 +14435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15">
       <c r="A255" s="11" t="s">
         <v>49</v>
       </c>
@@ -14487,12 +14492,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17">
       <c r="A257" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17">
       <c r="A259" s="14" t="s">
         <v>182</v>
       </c>
@@ -14533,7 +14538,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17">
       <c r="B260">
         <v>0.55000000000000004</v>
       </c>
@@ -14568,7 +14573,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17">
       <c r="A262" s="10" t="s">
         <v>87</v>
       </c>
@@ -14612,7 +14617,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17">
       <c r="A263" s="1">
         <v>1896</v>
       </c>
@@ -14669,7 +14674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17">
       <c r="A264" s="1">
         <f>A263+1</f>
         <v>1897</v>
@@ -14727,7 +14732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17">
       <c r="A265" s="1">
         <f t="shared" ref="A265:A282" si="179">A264+1</f>
         <v>1898</v>
@@ -14785,7 +14790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17">
       <c r="A266" s="1">
         <f t="shared" si="179"/>
         <v>1899</v>
@@ -14843,7 +14848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17">
       <c r="A267" s="1">
         <f t="shared" si="179"/>
         <v>1900</v>
@@ -14901,7 +14906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17">
       <c r="A268" s="1">
         <f t="shared" si="179"/>
         <v>1901</v>
@@ -14960,7 +14965,7 @@
       </c>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17">
       <c r="A269" s="1">
         <f t="shared" si="179"/>
         <v>1902</v>
@@ -15018,7 +15023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17">
       <c r="A270" s="1">
         <f t="shared" si="179"/>
         <v>1903</v>
@@ -15076,7 +15081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17">
       <c r="A271" s="1">
         <f t="shared" si="179"/>
         <v>1904</v>
@@ -15134,7 +15139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17">
       <c r="A272" s="1">
         <f t="shared" si="179"/>
         <v>1905</v>
@@ -15192,7 +15197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15">
       <c r="A273" s="1">
         <f t="shared" si="179"/>
         <v>1906</v>
@@ -15250,7 +15255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15">
       <c r="A274" s="1">
         <f t="shared" si="179"/>
         <v>1907</v>
@@ -15308,7 +15313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15">
       <c r="A275" s="1">
         <f t="shared" si="179"/>
         <v>1908</v>
@@ -15366,7 +15371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15">
       <c r="A276" s="1">
         <f t="shared" si="179"/>
         <v>1909</v>
@@ -15424,7 +15429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15">
       <c r="A277" s="1">
         <f t="shared" si="179"/>
         <v>1910</v>
@@ -15482,7 +15487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15">
       <c r="A278" s="1">
         <f t="shared" si="179"/>
         <v>1911</v>
@@ -15540,7 +15545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15">
       <c r="A279" s="1">
         <f t="shared" si="179"/>
         <v>1912</v>
@@ -15598,7 +15603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15">
       <c r="A280" s="1">
         <f t="shared" si="179"/>
         <v>1913</v>
@@ -15656,7 +15661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15">
       <c r="A281" s="1">
         <f t="shared" si="179"/>
         <v>1914</v>
@@ -15714,7 +15719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15">
       <c r="A282" s="1">
         <f t="shared" si="179"/>
         <v>1915</v>
@@ -15772,7 +15777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15">
       <c r="A283" s="1">
         <v>1916</v>
       </c>
@@ -15829,7 +15834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15">
       <c r="A284" s="11" t="s">
         <v>49</v>
       </c>
@@ -15886,12 +15891,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15">
       <c r="A286" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15">
       <c r="A288" s="10" t="s">
         <v>87</v>
       </c>
@@ -15935,7 +15940,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15">
       <c r="A289" s="1">
         <v>1896</v>
       </c>
@@ -15992,7 +15997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15">
       <c r="A290" s="1">
         <f>A289+1</f>
         <v>1897</v>
@@ -16050,7 +16055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15">
       <c r="A291" s="1">
         <f t="shared" ref="A291:A308" si="203">A290+1</f>
         <v>1898</v>
@@ -16108,7 +16113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15">
       <c r="A292" s="1">
         <f t="shared" si="203"/>
         <v>1899</v>
@@ -16166,7 +16171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15">
       <c r="A293" s="1">
         <f t="shared" si="203"/>
         <v>1900</v>
@@ -16224,7 +16229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15">
       <c r="A294" s="1">
         <f t="shared" si="203"/>
         <v>1901</v>
@@ -16282,7 +16287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15">
       <c r="A295" s="1">
         <f t="shared" si="203"/>
         <v>1902</v>
@@ -16340,7 +16345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15">
       <c r="A296" s="1">
         <f t="shared" si="203"/>
         <v>1903</v>
@@ -16398,7 +16403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15">
       <c r="A297" s="1">
         <f t="shared" si="203"/>
         <v>1904</v>
@@ -16456,7 +16461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15">
       <c r="A298" s="1">
         <f t="shared" si="203"/>
         <v>1905</v>
@@ -16514,7 +16519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15">
       <c r="A299" s="1">
         <f t="shared" si="203"/>
         <v>1906</v>
@@ -16572,7 +16577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15">
       <c r="A300" s="1">
         <f t="shared" si="203"/>
         <v>1907</v>
@@ -16630,7 +16635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15">
       <c r="A301" s="1">
         <f t="shared" si="203"/>
         <v>1908</v>
@@ -16688,7 +16693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15">
       <c r="A302" s="1">
         <f t="shared" si="203"/>
         <v>1909</v>
@@ -16746,7 +16751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15">
       <c r="A303" s="1">
         <f t="shared" si="203"/>
         <v>1910</v>
@@ -16804,7 +16809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15">
       <c r="A304" s="1">
         <f t="shared" si="203"/>
         <v>1911</v>
@@ -16862,7 +16867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15">
       <c r="A305" s="1">
         <f t="shared" si="203"/>
         <v>1912</v>
@@ -16920,7 +16925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15">
       <c r="A306" s="1">
         <f t="shared" si="203"/>
         <v>1913</v>
@@ -16978,7 +16983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15">
       <c r="A307" s="1">
         <f t="shared" si="203"/>
         <v>1914</v>
@@ -17036,7 +17041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15">
       <c r="A308" s="1">
         <f t="shared" si="203"/>
         <v>1915</v>
@@ -17094,7 +17099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15">
       <c r="A309" s="1">
         <v>1916</v>
       </c>
@@ -17151,7 +17156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15">
       <c r="A310" s="11" t="s">
         <v>49</v>
       </c>
@@ -17220,26 +17225,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F1B77F-63AA-4843-B8D8-CA14FF4F0797}">
   <dimension ref="A1:P99"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="13.42578125" customWidth="1"/>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
-    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.41796875" customWidth="1"/>
+    <col min="2" max="2" width="17.41796875" customWidth="1"/>
+    <col min="3" max="3" width="10.68359375" customWidth="1"/>
+    <col min="4" max="4" width="14.26171875" customWidth="1"/>
+    <col min="9" max="9" width="12.26171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="57.6">
       <c r="A4" s="2" t="s">
         <v>117</v>
       </c>
@@ -17274,7 +17279,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>118</v>
       </c>
@@ -17311,7 +17316,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>119</v>
       </c>
@@ -17348,7 +17353,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>120</v>
       </c>
@@ -17385,7 +17390,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>121</v>
       </c>
@@ -17422,7 +17427,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>122</v>
       </c>
@@ -17459,7 +17464,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>123</v>
       </c>
@@ -17496,7 +17501,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>124</v>
       </c>
@@ -17533,7 +17538,7 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>125</v>
       </c>
@@ -17570,7 +17575,7 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>126</v>
       </c>
@@ -17607,7 +17612,7 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13">
       <c r="A14" s="22" t="s">
         <v>129</v>
       </c>
@@ -17654,7 +17659,7 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13">
       <c r="A15" s="22" t="s">
         <v>130</v>
       </c>
@@ -17700,7 +17705,7 @@
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13">
       <c r="A16" s="17" t="s">
         <v>127</v>
       </c>
@@ -17745,7 +17750,7 @@
         <v>1395970</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16">
       <c r="A17" s="24" t="s">
         <v>128</v>
       </c>
@@ -17790,7 +17795,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16">
       <c r="A18" s="33" t="s">
         <v>185</v>
       </c>
@@ -17835,7 +17840,7 @@
         <v>566899</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16">
       <c r="A19" s="33" t="s">
         <v>186</v>
       </c>
@@ -17880,7 +17885,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16">
       <c r="A22" t="s">
         <v>196</v>
       </c>
@@ -17895,7 +17900,7 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16">
       <c r="A23" t="s">
         <v>194</v>
       </c>
@@ -17910,7 +17915,7 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -17922,7 +17927,7 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16">
       <c r="A25" s="36" t="s">
         <v>117</v>
       </c>
@@ -17953,7 +17958,7 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16">
       <c r="A26" t="s">
         <v>119</v>
       </c>
@@ -17977,7 +17982,7 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16">
       <c r="A27" t="s">
         <v>120</v>
       </c>
@@ -18003,7 +18008,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16">
       <c r="A28" t="s">
         <v>121</v>
       </c>
@@ -18029,7 +18034,7 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16">
       <c r="A29" t="s">
         <v>122</v>
       </c>
@@ -18055,7 +18060,7 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16">
       <c r="A30" s="21" t="s">
         <v>123</v>
       </c>
@@ -18086,7 +18091,7 @@
       <c r="O30" s="4"/>
       <c r="P30" s="4"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -18121,7 +18126,7 @@
       <c r="O31" s="4"/>
       <c r="P31" s="4"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -18154,7 +18159,7 @@
       <c r="O32" s="4"/>
       <c r="P32" s="4"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16">
       <c r="A33" t="s">
         <v>126</v>
       </c>
@@ -18189,7 +18194,7 @@
       <c r="O33" s="4"/>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16">
       <c r="A34" s="27" t="s">
         <v>127</v>
       </c>
@@ -18233,7 +18238,7 @@
       <c r="O34" s="4"/>
       <c r="P34" s="4"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16">
       <c r="A35" s="22" t="s">
         <v>88</v>
       </c>
@@ -18277,7 +18282,7 @@
       <c r="O35" s="4"/>
       <c r="P35" s="4"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16">
       <c r="A36" s="33" t="s">
         <v>185</v>
       </c>
@@ -18312,7 +18317,7 @@
       <c r="O36" s="4"/>
       <c r="P36" s="4"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16">
       <c r="A37" s="33" t="s">
         <v>88</v>
       </c>
@@ -18337,49 +18342,49 @@
         <v>99.993052867676965</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16">
       <c r="A39" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16">
       <c r="A40" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" ht="43.2">
       <c r="A42" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B42" s="40" t="s">
+      <c r="B42" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="C42" s="40" t="s">
+      <c r="C42" s="39" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="40" t="s">
+      <c r="D42" s="39" t="s">
         <v>110</v>
       </c>
-      <c r="E42" s="40" t="s">
+      <c r="E42" s="39" t="s">
         <v>111</v>
       </c>
-      <c r="F42" s="40" t="s">
+      <c r="F42" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="G42" s="40" t="s">
+      <c r="G42" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="H42" s="40" t="s">
+      <c r="H42" s="39" t="s">
         <v>151</v>
       </c>
-      <c r="I42" s="41" t="s">
+      <c r="I42" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="J42" s="40" t="s">
+      <c r="J42" s="39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -18404,7 +18409,7 @@
         <v>33658</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16">
       <c r="A44" t="s">
         <v>120</v>
       </c>
@@ -18431,7 +18436,7 @@
         <v>69982</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16">
       <c r="A45" t="s">
         <v>121</v>
       </c>
@@ -18458,7 +18463,7 @@
         <v>189850</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16">
       <c r="A46" t="s">
         <v>122</v>
       </c>
@@ -18485,7 +18490,7 @@
         <v>314861</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16">
       <c r="A47" s="21" t="s">
         <v>123</v>
       </c>
@@ -18512,7 +18517,7 @@
         <v>276883</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16">
       <c r="A48" t="s">
         <v>124</v>
       </c>
@@ -18541,7 +18546,7 @@
         <v>713875</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
         <v>125</v>
       </c>
@@ -18568,7 +18573,7 @@
         <v>1047253</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10">
       <c r="A50" t="s">
         <v>126</v>
       </c>
@@ -18597,7 +18602,7 @@
         <v>1048709</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10">
       <c r="A51" s="27" t="s">
         <v>127</v>
       </c>
@@ -18638,78 +18643,78 @@
         <v>3086720</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10">
       <c r="A52" s="22" t="s">
         <v>88</v>
       </c>
       <c r="B52" s="23">
-        <f>100*B51/$J51</f>
+        <f t="shared" ref="B52:J52" si="19">100*B51/$J51</f>
         <v>3.162645137880987</v>
       </c>
       <c r="C52" s="23">
-        <f>100*C51/$J51</f>
+        <f t="shared" si="19"/>
         <v>89.744680437487048</v>
       </c>
       <c r="D52" s="23">
-        <f>100*D51/$J51</f>
+        <f t="shared" si="19"/>
         <v>4.7382658614969939</v>
       </c>
       <c r="E52" s="23">
-        <f>100*E51/$J51</f>
+        <f t="shared" si="19"/>
         <v>1.7576586149699358</v>
       </c>
       <c r="F52" s="23">
-        <f>100*F51/$J51</f>
+        <f t="shared" si="19"/>
         <v>8.7471490773377569E-4</v>
       </c>
       <c r="G52" s="23">
-        <f>100*G51/$J51</f>
+        <f t="shared" si="19"/>
         <v>0.27236030478955009</v>
       </c>
       <c r="H52" s="23">
-        <f>100*H51/$J51</f>
+        <f t="shared" si="19"/>
         <v>1.308832676757205E-2</v>
       </c>
       <c r="I52" s="23">
-        <f>100*I51/$J51</f>
+        <f t="shared" si="19"/>
         <v>0.3104266017001866</v>
       </c>
       <c r="J52" s="23">
-        <f>100*J51/$J51</f>
+        <f t="shared" si="19"/>
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10">
       <c r="A53" s="33" t="s">
         <v>185</v>
       </c>
       <c r="B53" s="34"/>
       <c r="C53" s="34">
-        <f>SUM(C44:C46)</f>
+        <f t="shared" ref="C53:I53" si="20">SUM(C44:C46)</f>
         <v>447806</v>
       </c>
       <c r="D53" s="34">
-        <f>SUM(D44:D46)</f>
+        <f t="shared" si="20"/>
         <v>15165</v>
       </c>
       <c r="E53" s="34">
-        <f>SUM(E44:E46)</f>
+        <f t="shared" si="20"/>
         <v>40799</v>
       </c>
       <c r="F53" s="34">
-        <f>SUM(F44:F46)</f>
+        <f t="shared" si="20"/>
         <v>35</v>
       </c>
       <c r="G53" s="34">
-        <f>SUM(G44:G46)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="H53" s="34">
-        <f>SUM(H44:H46)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="I53" s="34">
-        <f>SUM(I44:I46)</f>
+        <f t="shared" si="20"/>
         <v>70888</v>
       </c>
       <c r="J53" s="34">
@@ -18717,37 +18722,37 @@
         <v>574693</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10">
       <c r="A54" s="33" t="s">
         <v>88</v>
       </c>
       <c r="B54" s="35"/>
       <c r="C54" s="35">
-        <f>C53/$J53*100</f>
+        <f t="shared" ref="C54:I54" si="21">C53/$J53*100</f>
         <v>77.920907336612771</v>
       </c>
       <c r="D54" s="35">
-        <f>D53/$J53*100</f>
+        <f t="shared" si="21"/>
         <v>2.6388001941906372</v>
       </c>
       <c r="E54" s="35">
-        <f>E53/$J53*100</f>
+        <f t="shared" si="21"/>
         <v>7.099268653002559</v>
       </c>
       <c r="F54" s="35">
-        <f>F53/$J53*100</f>
+        <f t="shared" si="21"/>
         <v>6.0902081633150218E-3</v>
       </c>
       <c r="G54" s="35">
-        <f>G53/$J53*100</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H54" s="35">
-        <f>H53/$J53*100</f>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I54" s="35">
-        <f>I53/$J53*100</f>
+        <f t="shared" si="21"/>
         <v>12.334933608030722</v>
       </c>
       <c r="J54" s="35">
@@ -18755,12 +18760,12 @@
         <v>87.665066391969276</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10">
       <c r="A57" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10">
       <c r="A59" s="36" t="s">
         <v>19</v>
       </c>
@@ -18768,7 +18773,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10">
       <c r="A60">
         <v>1896</v>
       </c>
@@ -18776,7 +18781,7 @@
         <v>35639</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10">
       <c r="A61">
         <v>1897</v>
       </c>
@@ -18784,7 +18789,7 @@
         <v>28021</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10">
       <c r="A62">
         <v>1898</v>
       </c>
@@ -18792,7 +18797,7 @@
         <v>41907</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10">
       <c r="A63">
         <v>1899</v>
       </c>
@@ -18800,7 +18805,7 @@
         <v>65559</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10">
       <c r="A64">
         <v>1900</v>
       </c>
@@ -18808,7 +18813,7 @@
         <v>76085</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2">
       <c r="A65">
         <v>1901</v>
       </c>
@@ -18816,7 +18821,7 @@
         <v>83166</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2">
       <c r="A66">
         <v>1902</v>
       </c>
@@ -18824,7 +18829,7 @@
         <v>103114</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2">
       <c r="A67">
         <v>1903</v>
       </c>
@@ -18832,7 +18837,7 @@
         <v>125022</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2">
       <c r="A68">
         <v>1904</v>
       </c>
@@ -18840,7 +18845,7 @@
         <v>151739</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2">
       <c r="A69">
         <v>1905</v>
       </c>
@@ -18848,7 +18853,7 @@
         <v>186157</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2">
       <c r="A70">
         <v>1906</v>
       </c>
@@ -18856,7 +18861,7 @@
         <v>221400</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2">
       <c r="A71">
         <v>1907</v>
       </c>
@@ -18864,7 +18869,7 @@
         <v>186071</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2">
       <c r="A72">
         <v>1908</v>
       </c>
@@ -18872,7 +18877,7 @@
         <v>119541</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2">
       <c r="A73">
         <v>1909</v>
       </c>
@@ -18880,7 +18885,7 @@
         <v>141698</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2">
       <c r="A74">
         <v>1910</v>
       </c>
@@ -18888,7 +18893,7 @@
         <v>162676</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2">
       <c r="A75">
         <v>1911</v>
       </c>
@@ -18896,7 +18901,7 @@
         <v>144660</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2">
       <c r="A76">
         <v>1912</v>
       </c>
@@ -18904,7 +18909,7 @@
         <v>217990</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2">
       <c r="A77">
         <v>1913</v>
       </c>
@@ -18912,7 +18917,7 @@
         <v>261265</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2">
       <c r="A78">
         <v>1914</v>
       </c>
@@ -18920,7 +18925,7 @@
         <v>119358</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2">
       <c r="A79">
         <v>1915</v>
       </c>
@@ -18928,7 +18933,7 @@
         <v>3880</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2">
       <c r="A80">
         <v>1916</v>
       </c>
@@ -18936,7 +18941,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>49</v>
       </c>
@@ -18945,7 +18950,7 @@
         <v>2477253</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>123</v>
       </c>
@@ -18954,7 +18959,7 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>124</v>
       </c>
@@ -18963,7 +18968,7 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>125</v>
       </c>
@@ -18972,7 +18977,7 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>126</v>
       </c>
@@ -18981,7 +18986,7 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" s="36" t="s">
         <v>117</v>
       </c>
@@ -18999,12 +19004,12 @@
       </c>
       <c r="F89" s="38"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>119</v>
       </c>
       <c r="B90" s="4">
-        <f>K6</f>
+        <f t="shared" ref="B90:B97" si="22">K6</f>
         <v>27525</v>
       </c>
       <c r="C90" s="4">
@@ -19017,16 +19022,16 @@
       </c>
       <c r="E90" s="14"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>120</v>
       </c>
       <c r="B91" s="4">
-        <f>K7</f>
+        <f t="shared" si="22"/>
         <v>64393</v>
       </c>
       <c r="C91" s="4">
-        <f t="shared" ref="C91:C97" si="19">J44</f>
+        <f t="shared" ref="C91:C97" si="23">J44</f>
         <v>69982</v>
       </c>
       <c r="D91" s="26">
@@ -19034,54 +19039,54 @@
         <v>92.01366065559715</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>121</v>
       </c>
       <c r="B92" s="4">
-        <f>K8</f>
+        <f t="shared" si="22"/>
         <v>223248</v>
       </c>
       <c r="C92" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>189850</v>
       </c>
       <c r="D92" s="26">
-        <f t="shared" ref="D92:D97" si="20">B92/C92*100</f>
+        <f t="shared" ref="D92:D97" si="24">B92/C92*100</f>
         <v>117.59178298656833</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>122</v>
       </c>
       <c r="B93" s="4">
-        <f>K9</f>
+        <f t="shared" si="22"/>
         <v>279258</v>
       </c>
       <c r="C93" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>314861</v>
       </c>
       <c r="D93" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>88.692470645777021</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" s="21" t="s">
         <v>123</v>
       </c>
       <c r="B94" s="4">
-        <f>K10</f>
+        <f t="shared" si="22"/>
         <v>173914</v>
       </c>
       <c r="C94" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>276883</v>
       </c>
       <c r="D94" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>62.811367978532452</v>
       </c>
       <c r="E94" s="4">
@@ -19089,20 +19094,20 @@
         <v>247211</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>124</v>
       </c>
       <c r="B95" s="4">
-        <f>K11</f>
+        <f t="shared" si="22"/>
         <v>340174</v>
       </c>
       <c r="C95" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>713875</v>
       </c>
       <c r="D95" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>47.651759761863069</v>
       </c>
       <c r="E95" s="4">
@@ -19110,20 +19115,20 @@
         <v>649198</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>125</v>
       </c>
       <c r="B96" s="4">
-        <f>K12</f>
+        <f t="shared" si="22"/>
         <v>471971</v>
       </c>
       <c r="C96" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1047253</v>
       </c>
       <c r="D96" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>45.067524275413867</v>
       </c>
       <c r="E96" s="4">
@@ -19131,20 +19136,20 @@
         <v>831386</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
         <v>126</v>
       </c>
       <c r="B97" s="4">
-        <f>K13</f>
+        <f t="shared" si="22"/>
         <v>409911</v>
       </c>
       <c r="C97" s="4">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>1048709</v>
       </c>
       <c r="D97" s="26">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>39.087201502037267</v>
       </c>
       <c r="E97" s="4">
@@ -19152,10 +19157,10 @@
         <v>747153</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5">
       <c r="B98" s="4"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5">
       <c r="B99" s="4"/>
     </row>
   </sheetData>
@@ -19167,42 +19172,42 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D506FF2-5C72-4314-9474-BB1C48673607}">
   <dimension ref="A1:J37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.68359375" customWidth="1"/>
+    <col min="3" max="3" width="18.83984375" customWidth="1"/>
+    <col min="4" max="4" width="13.83984375" customWidth="1"/>
+    <col min="5" max="5" width="16.83984375" customWidth="1"/>
+    <col min="7" max="7" width="13.26171875" customWidth="1"/>
+    <col min="8" max="8" width="16.41796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10">
       <c r="B5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10">
       <c r="B6" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10">
       <c r="B8" t="s">
         <v>1</v>
       </c>
@@ -19210,7 +19215,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10">
       <c r="B10" s="1">
         <v>1908</v>
       </c>
@@ -19218,7 +19223,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10">
       <c r="B11" s="1">
         <v>1917</v>
       </c>
@@ -19226,7 +19231,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10">
       <c r="B12" s="1">
         <v>1918</v>
       </c>
@@ -19234,21 +19239,21 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B14" s="39" t="s">
+    <row r="14" spans="1:10">
+      <c r="B14" s="41" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39" t="s">
+      <c r="C14" s="41"/>
+      <c r="D14" s="41" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="39"/>
-      <c r="G14" s="39" t="s">
+      <c r="E14" s="41"/>
+      <c r="G14" s="41" t="s">
         <v>167</v>
       </c>
-      <c r="H14" s="39"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H14" s="41"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="14" t="s">
         <v>19</v>
       </c>
@@ -19274,7 +19279,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10">
       <c r="A16" s="8">
         <v>1896</v>
       </c>
@@ -19304,7 +19309,7 @@
         <v>0.76905150314611981</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10">
       <c r="A17" s="8">
         <f>A16+1</f>
         <v>1897</v>
@@ -19335,7 +19340,7 @@
         <v>1.1447260834014719</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10">
       <c r="A18" s="8">
         <f t="shared" ref="A18:A36" si="3">A17+1</f>
         <v>1898</v>
@@ -19366,7 +19371,7 @@
         <v>3.4542314335060449E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10">
       <c r="A19" s="8">
         <f t="shared" si="3"/>
         <v>1899</v>
@@ -19397,7 +19402,7 @@
         <v>1.0711553175210407</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10">
       <c r="A20" s="8">
         <f t="shared" si="3"/>
         <v>1900</v>
@@ -19428,7 +19433,7 @@
         <v>2.3305537737866153</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10">
       <c r="A21" s="8">
         <f t="shared" si="3"/>
         <v>1901</v>
@@ -19459,7 +19464,7 @@
         <v>5.4061158328222199</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10">
       <c r="A22" s="8">
         <f t="shared" si="3"/>
         <v>1902</v>
@@ -19490,7 +19495,7 @@
         <v>7.1772055188530857</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10">
       <c r="A23" s="8">
         <f t="shared" si="3"/>
         <v>1903</v>
@@ -19521,7 +19526,7 @@
         <v>5.5701523909616393</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10">
       <c r="A24" s="8">
         <f t="shared" si="3"/>
         <v>1904</v>
@@ -19552,7 +19557,7 @@
         <v>7.0417936438833264</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10">
       <c r="A25" s="8">
         <f t="shared" si="3"/>
         <v>1905</v>
@@ -19583,7 +19588,7 @@
         <v>5.8077684314695697</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10">
       <c r="A26" s="8">
         <f t="shared" si="3"/>
         <v>1906</v>
@@ -19614,7 +19619,7 @@
         <v>5.8372604461200126</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10">
       <c r="A27" s="8">
         <f t="shared" si="3"/>
         <v>1907</v>
@@ -19645,7 +19650,7 @@
         <v>8.159514105330457</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10">
       <c r="A28" s="8">
         <f t="shared" si="3"/>
         <v>1908</v>
@@ -19676,7 +19681,7 @@
         <v>13.693419551160137</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10">
       <c r="A29" s="8">
         <f t="shared" si="3"/>
         <v>1909</v>
@@ -19707,7 +19712,7 @@
         <v>9.1432480191529386</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10">
       <c r="A30" s="8">
         <f t="shared" si="3"/>
         <v>1910</v>
@@ -19738,7 +19743,7 @@
         <v>11.441897961534032</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" s="8">
         <f t="shared" si="3"/>
         <v>1911</v>
@@ -19769,7 +19774,7 @@
         <v>13.023456612462224</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10">
       <c r="A32" s="8">
         <f t="shared" si="3"/>
         <v>1912</v>
@@ -19800,7 +19805,7 @@
         <v>13.15820198482195</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10">
       <c r="A33" s="8">
         <f t="shared" si="3"/>
         <v>1913</v>
@@ -19831,7 +19836,7 @@
         <v>9.6225471121240762</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10">
       <c r="A34" s="8">
         <f t="shared" si="3"/>
         <v>1914</v>
@@ -19862,7 +19867,7 @@
         <v>12.839879154078551</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10">
       <c r="A35" s="8">
         <f t="shared" si="3"/>
         <v>1915</v>
@@ -19893,7 +19898,7 @@
         <v>5.8097109177659272</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10">
       <c r="A36" s="8">
         <f t="shared" si="3"/>
         <v>1916</v>
@@ -19924,7 +19929,7 @@
         <v>5.6818181818181817</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10">
       <c r="A37" s="8" t="s">
         <v>80</v>
       </c>
@@ -19971,14 +19976,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B1A41B-E56C-436F-BC19-85A66CBD0B6E}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="11" max="11" width="13.5703125" customWidth="1"/>
-    <col min="15" max="15" width="26.7109375" customWidth="1"/>
-    <col min="16" max="16" width="19.85546875" customWidth="1"/>
+    <col min="11" max="11" width="13.578125" customWidth="1"/>
+    <col min="15" max="15" width="26.68359375" customWidth="1"/>
+    <col min="16" max="16" width="19.83984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18">
       <c r="A1" s="10" t="s">
         <v>19</v>
       </c>
@@ -20023,7 +20028,7 @@
       </c>
       <c r="P1" s="10"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1896</v>
       </c>
@@ -20069,7 +20074,7 @@
       <c r="P2" s="4"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18">
       <c r="A3">
         <v>1897</v>
       </c>
@@ -20115,7 +20120,7 @@
       <c r="P3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18">
       <c r="A4">
         <v>1898</v>
       </c>
@@ -20161,7 +20166,7 @@
       <c r="P4" s="4"/>
       <c r="R4" s="4"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18">
       <c r="A5">
         <v>1899</v>
       </c>
@@ -20207,7 +20212,7 @@
       <c r="P5" s="4"/>
       <c r="R5" s="4"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>1900</v>
       </c>
@@ -20253,7 +20258,7 @@
       <c r="P6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18">
       <c r="A7">
         <v>1901</v>
       </c>
@@ -20299,7 +20304,7 @@
       <c r="P7" s="4"/>
       <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18">
       <c r="A8">
         <v>1902</v>
       </c>
@@ -20345,7 +20350,7 @@
       <c r="P8" s="4"/>
       <c r="R8" s="4"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18">
       <c r="A9">
         <v>1903</v>
       </c>
@@ -20391,7 +20396,7 @@
       <c r="P9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18">
       <c r="A10">
         <v>1904</v>
       </c>
@@ -20437,7 +20442,7 @@
       <c r="P10" s="4"/>
       <c r="R10" s="4"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18">
       <c r="A11">
         <v>1905</v>
       </c>
@@ -20483,7 +20488,7 @@
       <c r="P11" s="4"/>
       <c r="R11" s="4"/>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18">
       <c r="A12">
         <v>1906</v>
       </c>
@@ -20529,7 +20534,7 @@
       <c r="P12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18">
       <c r="A13">
         <v>1907</v>
       </c>
@@ -20575,7 +20580,7 @@
       <c r="P13" s="4"/>
       <c r="R13" s="4"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18">
       <c r="A14">
         <v>1908</v>
       </c>
@@ -20621,7 +20626,7 @@
       <c r="P14" s="4"/>
       <c r="R14" s="4"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18">
       <c r="A15">
         <v>1909</v>
       </c>
@@ -20667,7 +20672,7 @@
       <c r="P15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18">
       <c r="A16">
         <v>1910</v>
       </c>
@@ -20713,7 +20718,7 @@
       <c r="P16" s="4"/>
       <c r="R16" s="4"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18">
       <c r="A17">
         <v>1911</v>
       </c>
@@ -20759,7 +20764,7 @@
       <c r="P17" s="4"/>
       <c r="R17" s="4"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18">
       <c r="A18">
         <v>1912</v>
       </c>
@@ -20805,7 +20810,7 @@
       <c r="P18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18">
       <c r="A19">
         <v>1913</v>
       </c>
@@ -20851,7 +20856,7 @@
       <c r="P19" s="4"/>
       <c r="R19" s="4"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18">
       <c r="A20">
         <v>1914</v>
       </c>
@@ -20897,7 +20902,7 @@
       <c r="P20" s="4"/>
       <c r="R20" s="4"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18">
       <c r="A21">
         <v>1915</v>
       </c>
@@ -20943,7 +20948,7 @@
       <c r="P21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18">
       <c r="A22">
         <v>1916</v>
       </c>
@@ -20989,10 +20994,10 @@
       <c r="P22" s="4"/>
       <c r="R22" s="4"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18">
       <c r="R24" s="4"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18">
       <c r="F26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -21004,6 +21009,6 @@
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+  <clbl:label id="{44ba9367-eb51-4860-91fd-089945178738}" enabled="1" method="Privileged" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
 </clbl:labelList>
 </file>